--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G22" t="n">

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU28"/>
+  <dimension ref="A1:AU29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1314,27 +1314,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>46206.5</v>
+        <v>46206.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1473,27 +1473,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46206.54166666666</v>
+        <v>46206.5</v>
       </c>
     </row>
     <row r="8">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>46206.58333333334</v>
+        <v>46206.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="AU14" s="3" t="n">
-        <v>46206.625</v>
+        <v>46206.58333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AU15" s="3" t="n">
-        <v>46206.65625</v>
+        <v>46206.625</v>
       </c>
     </row>
     <row r="16">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="AU23" s="3" t="n">
-        <v>46206.66666666666</v>
+        <v>46206.65625</v>
       </c>
     </row>
     <row r="24">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>46206.67708333334</v>
+        <v>46206.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="AU25" s="3" t="n">
-        <v>46206.83333333334</v>
+        <v>46206.67708333334</v>
       </c>
     </row>
     <row r="26">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>46206.875</v>
+        <v>46206.83333333334</v>
       </c>
     </row>
     <row r="27">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="AU27" s="3" t="n">
-        <v>46206.9375</v>
+        <v>46206.875</v>
       </c>
     </row>
     <row r="28">
@@ -4812,156 +4812,315 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Denver Summit W</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" s="3" t="n">
+        <v>46206.9375</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" s="3" t="n">
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" s="3" t="n">
         <v>46206.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>6.44</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.03</v>
+        <v>1.45</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>6.25</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>6.44</v>
+        <v>4.11</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.46</v>
+        <v>4.05</v>
       </c>
       <c r="O18" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
         <v>1.74</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.45</v>
+        <v>4.03</v>
       </c>
       <c r="O19" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="P19" t="n">
-        <v>6.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.71</v>
+        <v>4.46</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="P22" t="n">
-        <v>4.11</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>6.44</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.45</v>
+        <v>4.46</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>3.72</v>
       </c>
       <c r="P16" t="n">
-        <v>6.25</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
-        <v>4.11</v>
+        <v>6.25</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.03</v>
+        <v>2.29</v>
       </c>
       <c r="O19" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>2.91</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.29</v>
+        <v>4.05</v>
       </c>
       <c r="O20" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.91</v>
+        <v>1.74</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.46</v>
+        <v>1.43</v>
       </c>
       <c r="O22" t="n">
-        <v>3.72</v>
+        <v>4.7</v>
       </c>
       <c r="P22" t="n">
-        <v>1.74</v>
+        <v>6.44</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="O23" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="P23" t="n">
-        <v>6.44</v>
+        <v>4.11</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.46</v>
+        <v>1.43</v>
       </c>
       <c r="O16" t="n">
-        <v>3.72</v>
+        <v>4.7</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>6.44</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.45</v>
+        <v>2.29</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>3.14</v>
       </c>
       <c r="P17" t="n">
-        <v>6.25</v>
+        <v>2.91</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.29</v>
+        <v>1.71</v>
       </c>
       <c r="O19" t="n">
-        <v>3.14</v>
+        <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.91</v>
+        <v>4.11</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P20" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.03</v>
+        <v>4.46</v>
       </c>
       <c r="O21" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6.44</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="O23" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="P23" t="n">
-        <v>4.11</v>
+        <v>6.25</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.43</v>
+        <v>4.03</v>
       </c>
       <c r="O16" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>6.44</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.29</v>
+        <v>1.45</v>
       </c>
       <c r="O17" t="n">
-        <v>3.14</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.91</v>
+        <v>6.25</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.71</v>
+        <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="P19" t="n">
-        <v>4.11</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.03</v>
+        <v>2.29</v>
       </c>
       <c r="O20" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="P20" t="n">
-        <v>1.71</v>
+        <v>2.91</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.46</v>
+        <v>1.43</v>
       </c>
       <c r="O21" t="n">
-        <v>3.72</v>
+        <v>4.7</v>
       </c>
       <c r="P21" t="n">
-        <v>1.74</v>
+        <v>6.44</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.03</v>
+        <v>2.29</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>2.91</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.45</v>
+        <v>4.05</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>6.25</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.05</v>
+        <v>1.71</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>4.11</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.46</v>
+        <v>4.03</v>
       </c>
       <c r="O19" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.29</v>
+        <v>1.45</v>
       </c>
       <c r="O20" t="n">
-        <v>3.14</v>
+        <v>4.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.91</v>
+        <v>6.25</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.43</v>
+        <v>4.46</v>
       </c>
       <c r="O21" t="n">
-        <v>4.7</v>
+        <v>3.72</v>
       </c>
       <c r="P21" t="n">
-        <v>6.44</v>
+        <v>1.74</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>6.44</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.29</v>
+        <v>1.71</v>
       </c>
       <c r="O16" t="n">
-        <v>3.14</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.91</v>
+        <v>4.11</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="P18" t="n">
-        <v>4.11</v>
+        <v>6.25</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.03</v>
+        <v>2.29</v>
       </c>
       <c r="O19" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>2.91</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.46</v>
+        <v>4.03</v>
       </c>
       <c r="O21" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="P21" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.71</v>
+        <v>4.46</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="P16" t="n">
-        <v>4.11</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.05</v>
+        <v>2.29</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>2.91</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.45</v>
+        <v>4.05</v>
       </c>
       <c r="O18" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>6.25</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.29</v>
+        <v>1.45</v>
       </c>
       <c r="O19" t="n">
-        <v>3.14</v>
+        <v>4.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.91</v>
+        <v>6.25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.03</v>
+        <v>1.71</v>
       </c>
       <c r="O21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>4.11</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P14" t="n">
-        <v>5.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.46</v>
+        <v>1.43</v>
       </c>
       <c r="O16" t="n">
-        <v>3.72</v>
+        <v>4.7</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>6.44</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.29</v>
+        <v>1.45</v>
       </c>
       <c r="O17" t="n">
-        <v>3.14</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.91</v>
+        <v>6.25</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.05</v>
+        <v>4.46</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="P18" t="n">
         <v>1.74</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.03</v>
+        <v>2.29</v>
       </c>
       <c r="O20" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="P20" t="n">
-        <v>1.71</v>
+        <v>2.91</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P21" t="n">
         <v>1.71</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P21" t="n">
-        <v>4.11</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.43</v>
+        <v>4.05</v>
       </c>
       <c r="O23" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>6.44</v>
+        <v>1.74</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P13" t="n">
-        <v>5.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2519,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09</v>
+        <v>5.01</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="O16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>6.44</v>
+        <v>6.25</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.45</v>
+        <v>4.05</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>6.25</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.29</v>
+        <v>4.46</v>
       </c>
       <c r="O20" t="n">
-        <v>3.14</v>
+        <v>3.72</v>
       </c>
       <c r="P20" t="n">
-        <v>2.91</v>
+        <v>1.74</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.03</v>
+        <v>2.29</v>
       </c>
       <c r="O21" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>2.91</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="P22" t="n">
-        <v>4.11</v>
+        <v>6.44</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.05</v>
+        <v>1.71</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P23" t="n">
-        <v>1.74</v>
+        <v>4.11</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.21</v>
+        <v>1.61</v>
       </c>
       <c r="O9" t="n">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.83</v>
+        <v>4.36</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.45</v>
+        <v>2.29</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>3.14</v>
       </c>
       <c r="P16" t="n">
-        <v>6.25</v>
+        <v>2.91</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.03</v>
+        <v>1.43</v>
       </c>
       <c r="O19" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>6.44</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.46</v>
+        <v>1.45</v>
       </c>
       <c r="O20" t="n">
-        <v>3.72</v>
+        <v>4.6</v>
       </c>
       <c r="P20" t="n">
-        <v>1.74</v>
+        <v>6.25</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.29</v>
+        <v>4.46</v>
       </c>
       <c r="O21" t="n">
-        <v>3.14</v>
+        <v>3.72</v>
       </c>
       <c r="P21" t="n">
-        <v>2.91</v>
+        <v>1.74</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.43</v>
+        <v>4.03</v>
       </c>
       <c r="O22" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>6.44</v>
+        <v>1.71</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.71</v>
+        <v>4.05</v>
       </c>
       <c r="O23" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>4.11</v>
+        <v>1.74</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>2.21</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="P9" t="n">
-        <v>4.36</v>
+        <v>2.83</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.09</v>
+        <v>5.01</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2519,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P14" t="n">
-        <v>5.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.29</v>
+        <v>5.21</v>
       </c>
       <c r="O16" t="n">
-        <v>3.14</v>
+        <v>4.05</v>
       </c>
       <c r="P16" t="n">
-        <v>2.91</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.46</v>
+        <v>4.03</v>
       </c>
       <c r="O21" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="P21" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.03</v>
+        <v>2.29</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>1.71</v>
+        <v>2.91</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.21</v>
+        <v>1.61</v>
       </c>
       <c r="O9" t="n">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.83</v>
+        <v>4.36</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.46</v>
+        <v>1.45</v>
       </c>
       <c r="O17" t="n">
-        <v>3.72</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>6.25</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.71</v>
+        <v>2.29</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="P18" t="n">
-        <v>4.11</v>
+        <v>2.91</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>4.7</v>
+        <v>3.72</v>
       </c>
       <c r="P19" t="n">
-        <v>6.44</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="O20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P20" t="n">
-        <v>6.25</v>
+        <v>6.44</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.29</v>
+        <v>1.71</v>
       </c>
       <c r="O22" t="n">
-        <v>3.14</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.91</v>
+        <v>4.11</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>1.61</v>
       </c>
       <c r="O12" t="n">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.83</v>
+        <v>4.36</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P13" t="n">
-        <v>5.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2519,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09</v>
+        <v>5.01</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P17" t="n">
-        <v>6.25</v>
+        <v>6.44</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.46</v>
+        <v>1.71</v>
       </c>
       <c r="O19" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>4.11</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="O20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P20" t="n">
-        <v>6.44</v>
+        <v>6.25</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.03</v>
+        <v>4.46</v>
       </c>
       <c r="O21" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.71</v>
+        <v>4.05</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P22" t="n">
-        <v>4.11</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P23" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.21</v>
+        <v>4.03</v>
       </c>
       <c r="O16" t="n">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.43</v>
+        <v>4.05</v>
       </c>
       <c r="O17" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>6.44</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.29</v>
+        <v>1.45</v>
       </c>
       <c r="O18" t="n">
-        <v>3.14</v>
+        <v>4.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.91</v>
+        <v>6.25</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.71</v>
+        <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="P19" t="n">
-        <v>4.11</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.45</v>
+        <v>5.21</v>
       </c>
       <c r="O20" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="P20" t="n">
-        <v>6.25</v>
+        <v>1.59</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.46</v>
+        <v>1.71</v>
       </c>
       <c r="O21" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>1.74</v>
+        <v>4.11</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.05</v>
+        <v>1.43</v>
       </c>
       <c r="O22" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="P22" t="n">
-        <v>1.74</v>
+        <v>6.44</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.03</v>
+        <v>2.29</v>
       </c>
       <c r="O23" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="P23" t="n">
-        <v>1.71</v>
+        <v>2.91</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>1.61</v>
       </c>
       <c r="O11" t="n">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.83</v>
+        <v>4.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.03</v>
+        <v>1.45</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>6.25</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.05</v>
+        <v>4.46</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="P17" t="n">
         <v>1.74</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="O18" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>6.25</v>
+        <v>4.11</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.46</v>
+        <v>4.03</v>
       </c>
       <c r="O19" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="P21" t="n">
-        <v>4.11</v>
+        <v>6.44</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.43</v>
+        <v>2.29</v>
       </c>
       <c r="O22" t="n">
-        <v>4.7</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>6.44</v>
+        <v>2.91</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.29</v>
+        <v>4.05</v>
       </c>
       <c r="O23" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.91</v>
+        <v>1.74</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.09</v>
+        <v>5.01</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2519,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P14" t="n">
-        <v>5.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>6.25</v>
+        <v>4.11</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.46</v>
+        <v>4.05</v>
       </c>
       <c r="O17" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
         <v>1.74</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P18" t="n">
         <v>1.71</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P18" t="n">
-        <v>4.11</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.03</v>
+        <v>1.45</v>
       </c>
       <c r="O19" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>6.25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>5.21</v>
+        <v>2.29</v>
       </c>
       <c r="O20" t="n">
-        <v>4.05</v>
+        <v>3.14</v>
       </c>
       <c r="P20" t="n">
-        <v>1.59</v>
+        <v>2.91</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.43</v>
+        <v>5.21</v>
       </c>
       <c r="O21" t="n">
-        <v>4.7</v>
+        <v>4.05</v>
       </c>
       <c r="P21" t="n">
-        <v>6.44</v>
+        <v>1.59</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.29</v>
+        <v>4.46</v>
       </c>
       <c r="O22" t="n">
-        <v>3.14</v>
+        <v>3.72</v>
       </c>
       <c r="P22" t="n">
-        <v>2.91</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.05</v>
+        <v>1.43</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="P23" t="n">
-        <v>1.74</v>
+        <v>6.44</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.03</v>
+        <v>4.46</v>
       </c>
       <c r="O18" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="O19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P19" t="n">
-        <v>6.25</v>
+        <v>6.44</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.29</v>
+        <v>1.45</v>
       </c>
       <c r="O20" t="n">
-        <v>3.14</v>
+        <v>4.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.91</v>
+        <v>6.25</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>5.21</v>
+        <v>2.29</v>
       </c>
       <c r="O21" t="n">
-        <v>4.05</v>
+        <v>3.14</v>
       </c>
       <c r="P21" t="n">
-        <v>1.59</v>
+        <v>2.91</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.46</v>
+        <v>5.21</v>
       </c>
       <c r="O22" t="n">
-        <v>3.72</v>
+        <v>4.05</v>
       </c>
       <c r="P22" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.43</v>
+        <v>4.05</v>
       </c>
       <c r="O23" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>6.44</v>
+        <v>1.74</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.71</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P16" t="n">
-        <v>4.11</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.03</v>
+        <v>4.05</v>
       </c>
       <c r="O17" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.46</v>
+        <v>2.29</v>
       </c>
       <c r="O18" t="n">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>2.91</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.45</v>
+        <v>5.21</v>
       </c>
       <c r="O20" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="P20" t="n">
-        <v>6.25</v>
+        <v>1.59</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.29</v>
+        <v>1.45</v>
       </c>
       <c r="O21" t="n">
-        <v>3.14</v>
+        <v>4.6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.91</v>
+        <v>6.25</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>5.21</v>
+        <v>4.46</v>
       </c>
       <c r="O22" t="n">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="P22" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.05</v>
+        <v>1.71</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P23" t="n">
-        <v>1.74</v>
+        <v>4.11</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>1.19</v>
       </c>
       <c r="O9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T9" t="n">
         <v>4.5</v>
       </c>
-      <c r="P9" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4.7</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.3</v>
       </c>
-      <c r="AB9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P13" t="n">
-        <v>5.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2519,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09</v>
+        <v>5.01</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.03</v>
+        <v>4.46</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.29</v>
+        <v>5.21</v>
       </c>
       <c r="O18" t="n">
-        <v>3.14</v>
+        <v>4.05</v>
       </c>
       <c r="P18" t="n">
-        <v>2.91</v>
+        <v>1.59</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>5.21</v>
+        <v>1.71</v>
       </c>
       <c r="O20" t="n">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>1.59</v>
+        <v>4.11</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.45</v>
+        <v>2.29</v>
       </c>
       <c r="O21" t="n">
-        <v>4.6</v>
+        <v>3.14</v>
       </c>
       <c r="P21" t="n">
-        <v>6.25</v>
+        <v>2.91</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.46</v>
+        <v>4.03</v>
       </c>
       <c r="O22" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="O23" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="P23" t="n">
-        <v>4.11</v>
+        <v>6.25</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4391,40 +4391,40 @@
         <v>2.39</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AC25" t="n">
         <v>1.75</v>
@@ -4433,13 +4433,13 @@
         <v>1.92</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4709,55 +4709,55 @@
         <v>7.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4868,34 +4868,34 @@
         <v>2.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA28" t="n">
         <v>1.74</v>
@@ -4904,19 +4904,19 @@
         <v>1.92</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5027,34 +5027,34 @@
         <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA29" t="n">
         <v>1.82</v>
@@ -5063,19 +5063,19 @@
         <v>1.84</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.19</v>
+        <v>1.61</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>10.4</v>
+        <v>4.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.59</v>
+        <v>1.93</v>
       </c>
       <c r="R9" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="S9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="V9" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.77</v>
+        <v>2.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>4</v>
+        <v>2.27</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P10" t="n">
-        <v>4.36</v>
+        <v>1.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.93</v>
+        <v>4.85</v>
       </c>
       <c r="R10" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T10" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.27</v>
+        <v>1.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="P11" t="n">
-        <v>1.58</v>
+        <v>2.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>1.19</v>
       </c>
       <c r="O12" t="n">
-        <v>3.74</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.83</v>
+        <v>10.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.93</v>
+        <v>1.59</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="S12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U12" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.69</v>
+        <v>1.77</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.51</v>
+        <v>4</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.09</v>
+        <v>5.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>2.51</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P14" t="n">
-        <v>5.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2960,34 +2960,34 @@
         <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA16" t="n">
         <v>1.77</v>
@@ -2996,19 +2996,19 @@
         <v>1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.05</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>4.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5.21</v>
+        <v>4.05</v>
       </c>
       <c r="O18" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3437,55 +3437,55 @@
         <v>6.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.71</v>
+        <v>5.21</v>
       </c>
       <c r="O20" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z20" t="n">
         <v>3.7</v>
       </c>
-      <c r="P20" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.29</v>
+        <v>4.03</v>
       </c>
       <c r="O21" t="n">
-        <v>3.14</v>
+        <v>3.75</v>
       </c>
       <c r="P21" t="n">
-        <v>2.91</v>
+        <v>1.71</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.03</v>
+        <v>2.29</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>1.71</v>
+        <v>2.91</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4073,55 +4073,55 @@
         <v>6.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4232,55 +4232,55 @@
         <v>3.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4550,55 +4550,55 @@
         <v>4.56</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>4.36</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z10" t="n">
         <v>5.1</v>
       </c>
-      <c r="O10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AA10" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.47</v>
+        <v>2.69</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>1.19</v>
       </c>
       <c r="O11" t="n">
-        <v>3.74</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.83</v>
+        <v>10.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.93</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="S11" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.69</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.51</v>
+        <v>4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.19</v>
+        <v>1.61</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="P12" t="n">
-        <v>10.4</v>
+        <v>4.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.59</v>
+        <v>1.93</v>
       </c>
       <c r="R12" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="S12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="V12" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.77</v>
+        <v>2.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>4</v>
+        <v>2.27</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.71</v>
+        <v>2.29</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="P17" t="n">
-        <v>4.11</v>
+        <v>2.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="O18" t="n">
         <v>4.05</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.6</v>
-      </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="U18" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>2.35</v>
       </c>
       <c r="AK18" t="n">
         <v>1.13</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,49 +3428,49 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="O19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P19" t="n">
-        <v>6.44</v>
+        <v>6.25</v>
       </c>
       <c r="Q19" t="n">
         <v>1.95</v>
       </c>
       <c r="R19" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U19" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="V19" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC19" t="n">
         <v>2.48</v>
@@ -3479,13 +3479,13 @@
         <v>1.43</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>5.21</v>
+        <v>1.43</v>
       </c>
       <c r="O20" t="n">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="P20" t="n">
-        <v>1.59</v>
+        <v>6.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.5</v>
+        <v>1.95</v>
       </c>
       <c r="R20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.25</v>
       </c>
-      <c r="S20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="V20" t="n">
+      <c r="AC20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.43</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.37</v>
       </c>
       <c r="AE20" t="n">
         <v>1.13</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>2.35</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.13</v>
+        <v>2.48</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.03</v>
+        <v>1.71</v>
       </c>
       <c r="O21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>4.11</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="R21" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="S21" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V21" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.95</v>
+        <v>1.19</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.2</v>
+        <v>1.82</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.29</v>
+        <v>4.05</v>
       </c>
       <c r="O22" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="P22" t="n">
-        <v>2.91</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.45</v>
+        <v>4.03</v>
       </c>
       <c r="O23" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="P23" t="n">
-        <v>6.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.95</v>
       </c>
-      <c r="R23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AK23" t="n">
-        <v>2.75</v>
+        <v>1.2</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>1.61</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.58</v>
+        <v>4.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.21</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3.74</v>
+        <v>4.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.83</v>
+        <v>1.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.93</v>
+        <v>4.85</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.51</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.19</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>3.74</v>
       </c>
       <c r="P11" t="n">
-        <v>10.4</v>
+        <v>2.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.59</v>
+        <v>2.93</v>
       </c>
       <c r="R11" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.84</v>
+        <v>1.41</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>2.69</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>4</v>
+        <v>1.51</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.61</v>
+        <v>1.19</v>
       </c>
       <c r="O12" t="n">
+        <v>6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T12" t="n">
         <v>4.5</v>
       </c>
-      <c r="P12" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4.7</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.3</v>
       </c>
-      <c r="AB12" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.46</v>
+        <v>2.29</v>
       </c>
       <c r="O16" t="n">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>2.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.29</v>
+        <v>4.03</v>
       </c>
       <c r="O17" t="n">
-        <v>3.14</v>
+        <v>3.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.91</v>
+        <v>1.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5.21</v>
+        <v>4.46</v>
       </c>
       <c r="O18" t="n">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="P18" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.5</v>
+        <v>5.02</v>
       </c>
       <c r="R18" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="U18" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
         <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>2.35</v>
+        <v>1.26</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,49 +3428,49 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="O19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P19" t="n">
-        <v>6.25</v>
+        <v>6.44</v>
       </c>
       <c r="Q19" t="n">
         <v>1.95</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="V19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>2.48</v>
@@ -3479,13 +3479,13 @@
         <v>1.43</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.43</v>
+        <v>4.05</v>
       </c>
       <c r="O20" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>6.44</v>
+        <v>1.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.95</v>
+        <v>5.1</v>
       </c>
       <c r="R20" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="S20" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T20" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="V20" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.4</v>
+        <v>3.74</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.48</v>
+        <v>2.95</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.48</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="P21" t="n">
-        <v>4.11</v>
+        <v>6.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="R21" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U21" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="V21" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
         <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="O22" t="n">
         <v>4.05</v>
       </c>
-      <c r="O22" t="n">
-        <v>3.6</v>
-      </c>
       <c r="P22" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="R22" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T22" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="U22" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="V22" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.2</v>
+        <v>2.35</v>
       </c>
       <c r="AK22" t="n">
         <v>1.13</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.03</v>
+        <v>1.71</v>
       </c>
       <c r="O23" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P23" t="n">
-        <v>1.71</v>
+        <v>4.11</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="R23" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="S23" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T23" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.95</v>
+        <v>1.19</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.2</v>
+        <v>1.82</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>1.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.58</v>
+        <v>4.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P9" t="n">
-        <v>4.36</v>
+        <v>1.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.93</v>
+        <v>4.85</v>
       </c>
       <c r="R9" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="S9" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.27</v>
+        <v>1.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>1.19</v>
       </c>
       <c r="O11" t="n">
-        <v>3.74</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.83</v>
+        <v>10.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.93</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="S11" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.69</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.51</v>
+        <v>4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.19</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>3.74</v>
       </c>
       <c r="P12" t="n">
-        <v>10.4</v>
+        <v>2.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.59</v>
+        <v>2.93</v>
       </c>
       <c r="R12" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T12" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="V12" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>1.41</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.77</v>
+        <v>2.69</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>4</v>
+        <v>1.51</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P13" t="n">
-        <v>5.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.11</v>
+        <v>3.14</v>
       </c>
       <c r="R13" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="S13" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="U13" t="n">
-        <v>2.47</v>
+        <v>1.93</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>1.83</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>6.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.51</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.88</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.13</v>
+        <v>3.27</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.06</v>
+        <v>1.41</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09</v>
+        <v>5.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.14</v>
+        <v>2.11</v>
       </c>
       <c r="R14" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="S14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.17</v>
       </c>
-      <c r="T14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Z14" t="n">
-        <v>6.85</v>
+        <v>4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>2.51</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.27</v>
+        <v>2.13</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.41</v>
+        <v>2.06</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.29</v>
+        <v>5.21</v>
       </c>
       <c r="O16" t="n">
-        <v>3.14</v>
+        <v>4.05</v>
       </c>
       <c r="P16" t="n">
-        <v>2.91</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.03</v>
+        <v>2.29</v>
       </c>
       <c r="O17" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="P17" t="n">
-        <v>1.71</v>
+        <v>2.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,49 +3428,49 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="O19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P19" t="n">
-        <v>6.44</v>
+        <v>6.25</v>
       </c>
       <c r="Q19" t="n">
         <v>1.95</v>
       </c>
       <c r="R19" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U19" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="V19" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC19" t="n">
         <v>2.48</v>
@@ -3479,13 +3479,13 @@
         <v>1.43</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.05</v>
+        <v>1.71</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>1.74</v>
+        <v>4.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.1</v>
+        <v>2.25</v>
       </c>
       <c r="R20" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="S20" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T20" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
         <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.74</v>
+        <v>4.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.13</v>
+        <v>1.82</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,49 +3746,49 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="O21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P21" t="n">
-        <v>6.25</v>
+        <v>6.44</v>
       </c>
       <c r="Q21" t="n">
         <v>1.95</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
         <v>2.48</v>
@@ -3797,13 +3797,13 @@
         <v>1.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>1.17</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>5.21</v>
+        <v>4.03</v>
       </c>
       <c r="O22" t="n">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S22" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK22" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.13</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.71</v>
+        <v>4.05</v>
       </c>
       <c r="O23" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>4.11</v>
+        <v>1.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.25</v>
+        <v>5.1</v>
       </c>
       <c r="R23" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="S23" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T23" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U23" t="n">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W23" t="n">
         <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.82</v>
+        <v>1.13</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z9" t="n">
         <v>5.1</v>
       </c>
-      <c r="O9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AA9" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.47</v>
+        <v>2.69</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.19</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="P11" t="n">
-        <v>10.4</v>
+        <v>1.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.59</v>
+        <v>4.85</v>
       </c>
       <c r="R11" t="n">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="W11" t="n">
         <v>1.17</v>
@@ -2189,31 +2189,31 @@
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AA11" t="n">
         <v>1.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>2.47</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>1.19</v>
       </c>
       <c r="O12" t="n">
-        <v>3.74</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.83</v>
+        <v>10.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.93</v>
+        <v>1.59</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="S12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U12" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.69</v>
+        <v>1.77</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.51</v>
+        <v>4</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2792,19 +2792,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -2813,10 +2813,10 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2825,31 +2825,31 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.21</v>
+        <v>1.45</v>
       </c>
       <c r="O16" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>1.59</v>
+        <v>6.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.5</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S16" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="V16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.43</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>2.35</v>
+        <v>1.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.13</v>
+        <v>2.75</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.29</v>
+        <v>1.43</v>
       </c>
       <c r="O17" t="n">
-        <v>3.14</v>
+        <v>4.7</v>
       </c>
       <c r="P17" t="n">
-        <v>2.91</v>
+        <v>6.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.46</v>
+        <v>1.71</v>
       </c>
       <c r="O18" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>4.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.02</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
         <v>1.21</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.45</v>
+        <v>5.21</v>
       </c>
       <c r="O19" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="P19" t="n">
-        <v>6.25</v>
+        <v>1.59</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.95</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T19" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="U19" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="V19" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.48</v>
+        <v>2.89</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>2.35</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.75</v>
+        <v>1.13</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.71</v>
+        <v>4.05</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>4.11</v>
+        <v>1.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.25</v>
+        <v>5.1</v>
       </c>
       <c r="R20" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="S20" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T20" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W20" t="n">
         <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.82</v>
+        <v>1.13</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.43</v>
+        <v>4.46</v>
       </c>
       <c r="O21" t="n">
-        <v>4.7</v>
+        <v>3.72</v>
       </c>
       <c r="P21" t="n">
-        <v>6.44</v>
+        <v>1.74</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.95</v>
+        <v>5.02</v>
       </c>
       <c r="R21" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="S21" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U21" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="V21" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.48</v>
+        <v>2.93</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.48</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.03</v>
+        <v>2.29</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>1.71</v>
+        <v>2.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P23" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="S23" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U23" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK23" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.13</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.61</v>
+        <v>2.21</v>
       </c>
       <c r="O8" t="n">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="P8" t="n">
-        <v>4.36</v>
+        <v>2.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.93</v>
+        <v>2.93</v>
       </c>
       <c r="R8" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="S8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.14</v>
       </c>
-      <c r="T8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.42</v>
+        <v>2.46</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.27</v>
+        <v>1.51</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.21</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.83</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>1.19</v>
       </c>
       <c r="O11" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.48</v>
+        <v>10.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.85</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
         <v>1.17</v>
@@ -2189,31 +2189,31 @@
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AA11" t="n">
         <v>1.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.47</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.19</v>
+        <v>1.61</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="P12" t="n">
-        <v>10.4</v>
+        <v>4.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.59</v>
+        <v>1.93</v>
       </c>
       <c r="R12" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="S12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="V12" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.77</v>
+        <v>2.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>4</v>
+        <v>2.27</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.45</v>
+        <v>2.29</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>3.14</v>
       </c>
       <c r="P16" t="n">
-        <v>6.25</v>
+        <v>2.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.43</v>
+        <v>4.03</v>
       </c>
       <c r="O17" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="P17" t="n">
-        <v>6.44</v>
+        <v>1.71</v>
       </c>
       <c r="Q17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.95</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AK17" t="n">
-        <v>2.48</v>
+        <v>1.2</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5.21</v>
+        <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="P19" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.5</v>
+        <v>5.02</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="U19" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="V19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
         <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>2.35</v>
+        <v>1.26</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.05</v>
+        <v>1.45</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="P20" t="n">
-        <v>1.74</v>
+        <v>6.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.1</v>
+        <v>1.95</v>
       </c>
       <c r="R20" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
         <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
         <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.95</v>
+        <v>2.48</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.13</v>
+        <v>2.75</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.46</v>
+        <v>1.43</v>
       </c>
       <c r="O21" t="n">
-        <v>3.72</v>
+        <v>4.7</v>
       </c>
       <c r="P21" t="n">
-        <v>1.74</v>
+        <v>6.44</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.02</v>
+        <v>1.95</v>
       </c>
       <c r="R21" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="V21" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.93</v>
+        <v>2.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.17</v>
+        <v>2.48</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.29</v>
+        <v>5.21</v>
       </c>
       <c r="O22" t="n">
-        <v>3.14</v>
+        <v>4.05</v>
       </c>
       <c r="P22" t="n">
-        <v>2.91</v>
+        <v>1.59</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.03</v>
+        <v>4.05</v>
       </c>
       <c r="O23" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.71</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.95</v>
+        <v>1.2</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.21</v>
+        <v>1.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.83</v>
+        <v>4.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.93</v>
+        <v>1.93</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="S8" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T8" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="V8" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="W8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.14</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.51</v>
+        <v>2.27</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.61</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="P12" t="n">
-        <v>4.36</v>
+        <v>2.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.93</v>
+        <v>2.93</v>
       </c>
       <c r="R12" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="S12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.14</v>
       </c>
-      <c r="T12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.42</v>
+        <v>2.46</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.27</v>
+        <v>1.51</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.29</v>
+        <v>4.05</v>
       </c>
       <c r="O16" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.91</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.03</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>1.71</v>
+        <v>4.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="R17" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.95</v>
+        <v>1.19</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.2</v>
+        <v>1.82</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.71</v>
+        <v>4.46</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="P18" t="n">
-        <v>4.11</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.25</v>
+        <v>5.02</v>
       </c>
       <c r="R18" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U18" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
         <v>1.21</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,65 +3428,65 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.46</v>
+        <v>5.21</v>
       </c>
       <c r="O19" t="n">
-        <v>3.72</v>
+        <v>4.05</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.02</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T19" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="U19" t="n">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
         <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.9</v>
       </c>
-      <c r="AC19" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.26</v>
+        <v>2.35</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.45</v>
+        <v>2.29</v>
       </c>
       <c r="O20" t="n">
-        <v>4.6</v>
+        <v>3.14</v>
       </c>
       <c r="P20" t="n">
-        <v>6.25</v>
+        <v>2.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>5.21</v>
+        <v>4.03</v>
       </c>
       <c r="O22" t="n">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S22" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK22" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.13</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.05</v>
+        <v>1.45</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="P23" t="n">
-        <v>1.74</v>
+        <v>6.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.1</v>
+        <v>1.95</v>
       </c>
       <c r="R23" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="S23" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T23" t="n">
         <v>3.1</v>
       </c>
       <c r="U23" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W23" t="n">
         <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.95</v>
+        <v>2.48</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.13</v>
+        <v>2.75</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.61</v>
+        <v>5.1</v>
       </c>
       <c r="O8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P8" t="n">
-        <v>4.36</v>
+        <v>1.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.93</v>
+        <v>4.85</v>
       </c>
       <c r="R8" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T8" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.27</v>
+        <v>1.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.48</v>
+        <v>4.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.85</v>
+        <v>1.93</v>
       </c>
       <c r="R10" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="V10" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="AC10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD10" t="n">
         <v>2</v>
       </c>
-      <c r="AD10" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.1</v>
+        <v>2.27</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.19</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>3.74</v>
       </c>
       <c r="P11" t="n">
-        <v>10.4</v>
+        <v>2.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.59</v>
+        <v>2.93</v>
       </c>
       <c r="R11" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.84</v>
+        <v>1.41</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>2.69</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>4</v>
+        <v>1.51</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>1.19</v>
       </c>
       <c r="O12" t="n">
-        <v>3.74</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.83</v>
+        <v>10.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.93</v>
+        <v>1.59</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="S12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U12" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.69</v>
+        <v>1.77</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.51</v>
+        <v>4</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.05</v>
+        <v>1.71</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>4.11</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.1</v>
+        <v>2.25</v>
       </c>
       <c r="R16" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="S16" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
         <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.74</v>
+        <v>4.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.13</v>
+        <v>1.82</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
-        <v>4.11</v>
+        <v>6.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W17" t="n">
         <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.46</v>
+        <v>4.05</v>
       </c>
       <c r="O18" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
         <v>1.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.02</v>
+        <v>5.1</v>
       </c>
       <c r="R18" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.33</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5.21</v>
+        <v>2.29</v>
       </c>
       <c r="O19" t="n">
-        <v>4.05</v>
+        <v>3.14</v>
       </c>
       <c r="P19" t="n">
-        <v>1.59</v>
+        <v>2.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.29</v>
+        <v>5.21</v>
       </c>
       <c r="O20" t="n">
-        <v>3.14</v>
+        <v>4.05</v>
       </c>
       <c r="P20" t="n">
-        <v>2.91</v>
+        <v>1.59</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.03</v>
+        <v>4.46</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="P22" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>5.02</v>
       </c>
       <c r="R22" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="U22" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>3.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.95</v>
+        <v>1.26</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.45</v>
+        <v>4.03</v>
       </c>
       <c r="O23" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="P23" t="n">
-        <v>6.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.95</v>
       </c>
-      <c r="R23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AK23" t="n">
-        <v>2.75</v>
+        <v>1.2</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1367,10 +1367,10 @@
         <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>4.9</v>
+        <v>4.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="R6" t="n">
         <v>2.04</v>
@@ -1382,7 +1382,7 @@
         <v>2.56</v>
       </c>
       <c r="U6" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
         <v>1.33</v>
@@ -1406,10 +1406,10 @@
         <v>1.73</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE6" t="n">
         <v>1.05</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.1</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T8" t="n">
         <v>4.4</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.17</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.7</v>
+        <v>6.75</v>
       </c>
       <c r="AA8" t="n">
         <v>1.36</v>
       </c>
       <c r="AB8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG8" t="n">
         <v>2.7</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.47</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1841,61 +1841,61 @@
         <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>4.36</v>
+        <v>1.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.85</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="AC10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.3</v>
       </c>
-      <c r="AB10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.8</v>
+        <v>1.89</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.27</v>
+        <v>1.12</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="O11" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S11" t="n">
         <v>1.22</v>
       </c>
       <c r="T11" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W11" t="n">
         <v>1.14</v>
@@ -2189,31 +2189,31 @@
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,43 +2315,43 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="P12" t="n">
-        <v>10.4</v>
+        <v>7</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="R12" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="S12" t="n">
         <v>1.17</v>
       </c>
       <c r="T12" t="n">
-        <v>4.5</v>
+        <v>3.86</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.4</v>
+        <v>5.95</v>
       </c>
       <c r="AA12" t="n">
         <v>1.36</v>
@@ -2363,16 +2363,16 @@
         <v>1.96</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF12" t="n">
         <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.77</v>
+        <v>1.99</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="O13" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
         <v>3.14</v>
       </c>
       <c r="R13" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="S13" t="n">
         <v>1.17</v>
@@ -2495,10 +2495,10 @@
         <v>4.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W13" t="n">
         <v>1.22</v>
@@ -2513,19 +2513,19 @@
         <v>6.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AC13" t="n">
         <v>1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AF13" t="n">
         <v>1.29</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,37 +2633,37 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="P14" t="n">
-        <v>5.01</v>
+        <v>3.98</v>
       </c>
       <c r="Q14" t="n">
         <v>2.11</v>
       </c>
       <c r="R14" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="V14" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
         <v>1.17</v>
@@ -2672,10 +2672,10 @@
         <v>4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC14" t="n">
         <v>2.51</v>
@@ -2684,13 +2684,13 @@
         <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF14" t="n">
         <v>1.64</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>4.45</v>
       </c>
       <c r="P16" t="n">
-        <v>4.11</v>
+        <v>5.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="AD16" t="n">
         <v>1.48</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.18</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK16" t="n">
-        <v>1.82</v>
+        <v>2.62</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.45</v>
+        <v>4.33</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>6.25</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.95</v>
+        <v>4.75</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
         <v>1.3</v>
@@ -3131,43 +3131,43 @@
         <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="V17" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z17" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.21</v>
+        <v>2.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.48</v>
+        <v>2.93</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
         <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.75</v>
+        <v>1.18</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
         <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>2.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.29</v>
+        <v>1.72</v>
       </c>
       <c r="O19" t="n">
-        <v>3.14</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.91</v>
+        <v>4.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>5.21</v>
+        <v>1.42</v>
       </c>
       <c r="O20" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="P20" t="n">
-        <v>1.59</v>
+        <v>6</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.5</v>
+        <v>1.85</v>
       </c>
       <c r="R20" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T20" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="U20" t="n">
-        <v>2.72</v>
+        <v>2.41</v>
       </c>
       <c r="V20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.43</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>2.35</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.13</v>
+        <v>2.48</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.43</v>
+        <v>2.48</v>
       </c>
       <c r="O21" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="P21" t="n">
-        <v>6.44</v>
+        <v>2.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.02</v>
+        <v>5.1</v>
       </c>
       <c r="R22" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T22" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2.88</v>
       </c>
-      <c r="U22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.93</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF22" t="n">
         <v>1.72</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4064,22 +4064,22 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.03</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P23" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>4.61</v>
       </c>
       <c r="R23" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T23" t="n">
         <v>3.15</v>
@@ -4091,13 +4091,13 @@
         <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
         <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z23" t="n">
         <v>3.95</v>
@@ -4118,10 +4118,10 @@
         <v>1.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AK23" t="n">
         <v>1.2</v>
@@ -4223,31 +4223,31 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>3.36</v>
+        <v>3.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="R24" t="n">
         <v>2.3</v>
       </c>
       <c r="S24" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T24" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U24" t="n">
         <v>2.34</v>
       </c>
       <c r="V24" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W24" t="n">
         <v>1.09</v>
@@ -4256,25 +4256,25 @@
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z24" t="n">
         <v>3.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.98</v>
+        <v>2.27</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF24" t="n">
         <v>1.52</v>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AK24" t="n">
         <v>1.62</v>
@@ -4382,34 +4382,34 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="O25" t="n">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="P25" t="n">
-        <v>2.39</v>
+        <v>2.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="R25" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="S25" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T25" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V25" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
@@ -4418,22 +4418,22 @@
         <v>1.04</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AF25" t="n">
         <v>1.28</v>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4541,25 +4541,25 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P26" t="n">
-        <v>4.56</v>
+        <v>4.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R26" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="S26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T26" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U26" t="n">
         <v>2.26</v>
@@ -4568,7 +4568,7 @@
         <v>1.56</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
@@ -4580,19 +4580,19 @@
         <v>4.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF26" t="n">
         <v>1.56</v>
@@ -4614,7 +4614,7 @@
         <v>1.16</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4709,22 +4709,22 @@
         <v>7.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="R27" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S27" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="T27" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W27" t="n">
         <v>1.12</v>
@@ -4733,31 +4733,31 @@
         <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z27" t="n">
         <v>4.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AK27" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4871,19 +4871,19 @@
         <v>3.1</v>
       </c>
       <c r="R28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U28" t="n">
         <v>2.3</v>
       </c>
-      <c r="S28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.45</v>
-      </c>
       <c r="V28" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W28" t="n">
         <v>1.09</v>
@@ -4892,31 +4892,31 @@
         <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
         <v>3.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AC28" t="n">
         <v>2.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE28" t="n">
         <v>1.12</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>1.24</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5030,7 +5030,7 @@
         <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S29" t="n">
         <v>1.34</v>
@@ -5042,40 +5042,40 @@
         <v>2.63</v>
       </c>
       <c r="V29" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X29" t="n">
         <v>1.05</v>
       </c>
-      <c r="X29" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU29"/>
+  <dimension ref="A1:AU28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -996,7 +996,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46206.375</v>
+        <v>46206.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1473,27 +1473,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46206.5</v>
+        <v>46206.54166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.85</v>
+        <v>1.65</v>
       </c>
       <c r="R9" t="n">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="S9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.17</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.7</v>
+        <v>5.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AE9" t="n">
         <v>1.27</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.48</v>
+        <v>1.84</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.1</v>
+        <v>3.42</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>2.35</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.35</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W11" t="n">
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.14</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="O12" t="n">
-        <v>5.75</v>
+        <v>3.78</v>
       </c>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>3.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.65</v>
+        <v>2.11</v>
       </c>
       <c r="R12" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.17</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Z12" t="n">
-        <v>5.95</v>
+        <v>4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.96</v>
+        <v>2.51</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.42</v>
+        <v>2.05</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>46206.54166666666</v>
+        <v>46206.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.63</v>
+        <v>2.88</v>
       </c>
       <c r="O14" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>3.98</v>
+        <v>2.19</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
         <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AD14" t="n">
         <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.05</v>
+        <v>1.32</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="AU14" s="3" t="n">
-        <v>46206.58333333334</v>
+        <v>46206.625</v>
       </c>
     </row>
     <row r="15">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P15" t="n">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>4.61</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
         <v>3.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AC15" t="n">
         <v>2.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AU15" s="3" t="n">
-        <v>46206.625</v>
+        <v>46206.65625</v>
       </c>
     </row>
     <row r="16">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="O16" t="n">
-        <v>4.45</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>5.75</v>
+        <v>4.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U16" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.62</v>
+        <v>1.82</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.33</v>
+        <v>1.44</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>5.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.75</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U17" t="n">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.99</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.93</v>
+        <v>2.48</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
         <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.18</v>
+        <v>2.62</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="P18" t="n">
-        <v>1.55</v>
+        <v>3.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="R18" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="U18" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.98</v>
+        <v>2.27</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.89</v>
+        <v>2.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.88</v>
+        <v>2.33</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>2.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.12</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.72</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P19" t="n">
-        <v>4.16</v>
+        <v>1.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T19" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE19" t="n">
         <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.2</v>
+        <v>2.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.82</v>
+        <v>1.12</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.42</v>
+        <v>4.33</v>
       </c>
       <c r="O20" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P20" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.85</v>
+        <v>4.75</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.48</v>
+        <v>1.18</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK21" t="n">
         <v>2.48</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>2.48</v>
       </c>
       <c r="O23" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="P23" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4176,12 +4176,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="P24" t="n">
-        <v>3.06</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S24" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T24" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="U24" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="V24" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.75</v>
+        <v>6.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.45</v>
+        <v>1.78</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.33</v>
+        <v>3.34</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>46206.66666666666</v>
+        <v>46206.67708333334</v>
       </c>
     </row>
     <row r="25">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.31</v>
+        <v>1.58</v>
       </c>
       <c r="O25" t="n">
-        <v>3.95</v>
+        <v>4.15</v>
       </c>
       <c r="P25" t="n">
-        <v>2.54</v>
+        <v>4.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="S25" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="T25" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="V25" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.59</v>
+        <v>2.39</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.34</v>
+        <v>2.23</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="AU25" s="3" t="n">
-        <v>46206.67708333334</v>
+        <v>46206.83333333334</v>
       </c>
     </row>
     <row r="26">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="O26" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>4.45</v>
+        <v>7.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="R26" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S26" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T26" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U26" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.23</v>
+        <v>1.8</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>46206.83333333334</v>
+        <v>46206.875</v>
       </c>
     </row>
     <row r="27">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>7.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S27" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T27" t="n">
-        <v>3.28</v>
+        <v>3.06</v>
       </c>
       <c r="U27" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V27" t="n">
         <v>1.5</v>
       </c>
       <c r="W27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.12</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AK27" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="AU27" s="3" t="n">
-        <v>46206.875</v>
+        <v>46206.9375</v>
       </c>
     </row>
     <row r="28">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
         <v>3.1</v>
@@ -4874,49 +4874,49 @@
         <v>2.2</v>
       </c>
       <c r="S28" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T28" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="V28" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4962,165 +4962,6 @@
         <v>0</v>
       </c>
       <c r="AU28" s="3" t="n">
-        <v>46206.9375</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46206</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Orlando Pride</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" s="3" t="n">
         <v>46206.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T8" t="n">
         <v>4</v>
       </c>
-      <c r="P8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4.4</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.75</v>
+        <v>5.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.92</v>
+        <v>2.69</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,31 +1838,31 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="O9" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="R9" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="S9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T9" t="n">
-        <v>3.86</v>
+        <v>4.4</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="V9" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="W9" t="n">
         <v>1.2</v>
@@ -1871,31 +1871,31 @@
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.95</v>
+        <v>6.75</v>
       </c>
       <c r="AA9" t="n">
         <v>1.36</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.99</v>
+        <v>2.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.42</v>
+        <v>2.2</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.85</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="S11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.7</v>
+        <v>5.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AE11" t="n">
         <v>1.27</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.48</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.1</v>
+        <v>3.42</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.63</v>
+        <v>2.62</v>
       </c>
       <c r="O12" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>3.98</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.11</v>
+        <v>3.14</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="U12" t="n">
-        <v>2.49</v>
+        <v>1.91</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>6.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.16</v>
+        <v>3.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.51</v>
+        <v>1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.15</v>
+        <v>3.27</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.05</v>
+        <v>1.43</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.62</v>
+        <v>1.63</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="P13" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG13" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W13" t="n">
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.22</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.43</v>
+        <v>2.05</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="O15" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
         <v>1.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.61</v>
+        <v>4.75</v>
       </c>
       <c r="R15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
         <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V15" t="n">
         <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
         <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="P16" t="n">
-        <v>4.16</v>
+        <v>3.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="R16" t="n">
         <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
         <v>3.4</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.82</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="P18" t="n">
-        <v>3.06</v>
+        <v>1.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.62</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.29</v>
       </c>
-      <c r="T18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.27</v>
+        <v>1.98</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.33</v>
+        <v>1.88</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.24</v>
+        <v>2.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>1.12</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="O19" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>6.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="R19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB19" t="n">
         <v>2.25</v>
       </c>
-      <c r="S19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="AC19" t="n">
         <v>2.75</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.89</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>2.17</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.12</v>
+        <v>2.48</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.33</v>
+        <v>2.48</v>
       </c>
       <c r="O20" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="P21" t="n">
-        <v>6.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.85</v>
+        <v>4.61</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T21" t="n">
         <v>3.15</v>
       </c>
       <c r="U21" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
         <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.48</v>
+        <v>1.2</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>1.72</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P22" t="n">
-        <v>1.65</v>
+        <v>4.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="R22" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="U22" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="V22" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.79</v>
+        <v>4.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC22" t="n">
         <v>2.88</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.77</v>
+        <v>1.2</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.14</v>
+        <v>1.82</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.48</v>
+        <v>4.5</v>
       </c>
       <c r="O23" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.85</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="S8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.17</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.7</v>
+        <v>5.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AE8" t="n">
         <v>1.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.48</v>
+        <v>1.84</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.1</v>
+        <v>3.42</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.55</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.87</v>
+        <v>2.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.7</v>
+        <v>1.89</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.2</v>
+        <v>1.12</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.35</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG10" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.14</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="O11" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="R11" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T11" t="n">
-        <v>3.86</v>
+        <v>4.4</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="V11" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="W11" t="n">
         <v>1.2</v>
@@ -2189,31 +2189,31 @@
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.95</v>
+        <v>6.75</v>
       </c>
       <c r="AA11" t="n">
         <v>1.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.99</v>
+        <v>2.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.42</v>
+        <v>2.2</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.33</v>
+        <v>1.72</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7</v>
+        <v>4.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.75</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
         <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U15" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC15" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.18</v>
+        <v>1.82</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="O16" t="n">
-        <v>3.82</v>
+        <v>3.15</v>
       </c>
       <c r="P16" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
-        <v>5.75</v>
+        <v>6.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="R17" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="U17" t="n">
         <v>2.41</v>
       </c>
       <c r="V17" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AF17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK17" t="n">
         <v>2.48</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.62</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="P18" t="n">
-        <v>1.57</v>
+        <v>3.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="R18" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="U18" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.98</v>
+        <v>2.27</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.89</v>
+        <v>2.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.88</v>
+        <v>2.33</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>2.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.12</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="P19" t="n">
-        <v>6.65</v>
+        <v>1.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.29</v>
       </c>
-      <c r="T19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.22</v>
-      </c>
       <c r="Z19" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>2.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.48</v>
+        <v>1.12</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.48</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.61</v>
+        <v>5.1</v>
       </c>
       <c r="R21" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S21" t="n">
         <v>1.3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="U21" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V21" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.95</v>
+        <v>3.79</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.72</v>
+        <v>4.33</v>
       </c>
       <c r="O22" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>4.16</v>
+        <v>1.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.3</v>
+        <v>4.75</v>
       </c>
       <c r="R22" t="n">
         <v>2.3</v>
       </c>
       <c r="S22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z22" t="n">
         <v>3.4</v>
       </c>
-      <c r="U22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AA22" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.82</v>
+        <v>1.18</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P23" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.1</v>
+        <v>4.61</v>
       </c>
       <c r="R23" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S23" t="n">
         <v>1.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="U23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.55</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="AD23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.1</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -899,31 +899,31 @@
         <v>2.53</v>
       </c>
       <c r="S3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
         <v>1.17</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
         <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
         <v>2.53</v>
@@ -938,10 +938,10 @@
         <v>1.26</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
         <v>1.52</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1403,22 +1403,22 @@
         <v>2.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
         <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.65</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="U7" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="V7" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.25</v>
+        <v>3.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.65</v>
+        <v>4.85</v>
       </c>
       <c r="R8" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="S8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.17</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.2</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.95</v>
+        <v>5.7</v>
       </c>
       <c r="AA8" t="n">
         <v>1.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="n">
         <v>1.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.84</v>
+        <v>1.48</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.99</v>
+        <v>2.45</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.42</v>
+        <v>1.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>2.35</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.85</v>
+        <v>1.64</v>
       </c>
       <c r="R10" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="S10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.08</v>
       </c>
-      <c r="Z10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.1</v>
+        <v>3.42</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="O15" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P15" t="n">
-        <v>4.16</v>
+        <v>5.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V15" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.82</v>
+        <v>2.62</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.48</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="P16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="P17" t="n">
-        <v>6.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.85</v>
+        <v>4.61</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
         <v>3.15</v>
       </c>
       <c r="U17" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
         <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.48</v>
+        <v>1.2</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>4.33</v>
       </c>
       <c r="O18" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>3.06</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.62</v>
+        <v>4.75</v>
       </c>
       <c r="R18" t="n">
         <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z18" t="n">
         <v>3.4</v>
       </c>
-      <c r="U18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AA18" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>1.72</v>
       </c>
       <c r="O19" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>4.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="U19" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
         <v>1.13</v>
       </c>
       <c r="AF19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.82</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.12</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="P20" t="n">
-        <v>5.75</v>
+        <v>3.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="R20" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="V20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W20" t="n">
         <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
         <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
         <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.62</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.33</v>
+        <v>2.48</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="O23" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="P23" t="n">
-        <v>1.7</v>
+        <v>6.65</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.61</v>
+        <v>1.85</v>
       </c>
       <c r="R23" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T23" t="n">
         <v>3.15</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
         <v>1.22</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.2</v>
+        <v>2.48</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4226,10 +4226,10 @@
         <v>2.31</v>
       </c>
       <c r="O24" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="P24" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
         <v>2.71</v>
@@ -4241,16 +4241,16 @@
         <v>1.17</v>
       </c>
       <c r="T24" t="n">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="U24" t="n">
         <v>1.85</v>
       </c>
       <c r="V24" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -4550,7 +4550,7 @@
         <v>7.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="R26" t="n">
         <v>2.4</v>
@@ -4562,34 +4562,34 @@
         <v>3.28</v>
       </c>
       <c r="U26" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V26" t="n">
         <v>1.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
         <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z26" t="n">
         <v>4.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE26" t="n">
         <v>1.11</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4709,7 +4709,7 @@
         <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="R27" t="n">
         <v>2.2</v>
@@ -4718,31 +4718,31 @@
         <v>1.3</v>
       </c>
       <c r="T27" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="U27" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="V27" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W27" t="n">
         <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC27" t="n">
         <v>2.8</v>
@@ -4751,13 +4751,13 @@
         <v>1.35</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF27" t="n">
         <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4874,10 +4874,10 @@
         <v>2.2</v>
       </c>
       <c r="S28" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="U28" t="n">
         <v>2.63</v>
@@ -4892,25 +4892,25 @@
         <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AC28" t="n">
         <v>2.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF28" t="n">
         <v>1.67</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -896,7 +896,7 @@
         <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="S3" t="n">
         <v>1.25</v>
@@ -926,16 +926,16 @@
         <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="AC3" t="n">
         <v>2.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AF3" t="n">
         <v>1.42</v>
@@ -1370,16 +1370,16 @@
         <v>4.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R6" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S6" t="n">
         <v>1.42</v>
       </c>
       <c r="T6" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
         <v>3</v>
@@ -1415,10 +1415,10 @@
         <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="R7" t="n">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88</v>
+        <v>3.82</v>
       </c>
       <c r="U7" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.48</v>
+        <v>5.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.88</v>
+        <v>2.69</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.97</v>
+        <v>1.98</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
         <v>4.33</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Q8" t="n">
-        <v>4.85</v>
+        <v>2.11</v>
       </c>
       <c r="R8" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="S8" t="n">
         <v>1.18</v>
       </c>
       <c r="T8" t="n">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.7</v>
+        <v>6.75</v>
       </c>
       <c r="AA8" t="n">
         <v>1.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.35</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.45</v>
+        <v>1.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.65</v>
+        <v>5.24</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="S9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.22</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Z9" t="n">
-        <v>5.25</v>
+        <v>3.48</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2000,22 +2000,22 @@
         <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="P10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="S10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T10" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="U10" t="n">
         <v>2.02</v>
@@ -2030,16 +2030,16 @@
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AC10" t="n">
         <v>1.96</v>
@@ -2051,10 +2051,10 @@
         <v>1.28</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.55</v>
       </c>
-      <c r="O11" t="n">
-        <v>4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.2</v>
+        <v>1.51</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="Q12" t="n">
         <v>3.14</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="S12" t="n">
         <v>1.17</v>
@@ -2354,13 +2354,13 @@
         <v>6.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AD12" t="n">
         <v>1.9</v>
@@ -2474,16 +2474,16 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="O13" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
         <v>2.3</v>
@@ -2492,10 +2492,10 @@
         <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
         <v>1.53</v>
@@ -2504,19 +2504,19 @@
         <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AC13" t="n">
         <v>2.51</v>
@@ -2531,7 +2531,7 @@
         <v>1.64</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.44</v>
+        <v>2.48</v>
       </c>
       <c r="O15" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>5.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,65 +2951,65 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="U16" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.98</v>
       </c>
-      <c r="AC16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>2.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,34 +3110,34 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>4.11</v>
       </c>
       <c r="O17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P17" t="n">
         <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.61</v>
+        <v>4.56</v>
       </c>
       <c r="R17" t="n">
         <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
         <v>3.15</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V17" t="n">
         <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
@@ -3146,28 +3146,28 @@
         <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.95</v>
+        <v>3.99</v>
       </c>
       <c r="AA17" t="n">
         <v>1.69</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AD17" t="n">
         <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
         <v>1.2</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.33</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="R18" t="n">
         <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U18" t="n">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AC18" t="n">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.72</v>
+        <v>1.39</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>4.65</v>
       </c>
       <c r="P19" t="n">
-        <v>4.16</v>
+        <v>6.54</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
         <v>1.28</v>
       </c>
       <c r="T19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.82</v>
+        <v>2.48</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="O20" t="n">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="P20" t="n">
-        <v>3.06</v>
+        <v>3.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="R20" t="n">
         <v>2.3</v>
       </c>
       <c r="S20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="U20" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="V20" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>1.44</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P21" t="n">
-        <v>1.65</v>
+        <v>6.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.1</v>
+        <v>1.91</v>
       </c>
       <c r="R21" t="n">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="S21" t="n">
         <v>1.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="U21" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.79</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.77</v>
+        <v>1.18</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.14</v>
+        <v>2.62</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.48</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="P22" t="n">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.4</v>
+        <v>5.35</v>
       </c>
       <c r="O23" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="P23" t="n">
-        <v>6.65</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T23" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="U23" t="n">
-        <v>2.41</v>
+        <v>2.72</v>
       </c>
       <c r="V23" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.08</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.17</v>
+        <v>2.17</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.48</v>
+        <v>1.12</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>2.31</v>
       </c>
       <c r="O24" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="P24" t="n">
         <v>2.5</v>
@@ -4247,10 +4247,10 @@
         <v>1.85</v>
       </c>
       <c r="V24" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -4262,7 +4262,7 @@
         <v>6.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AB24" t="n">
         <v>3</v>
@@ -4274,7 +4274,7 @@
         <v>1.98</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AF24" t="n">
         <v>1.28</v>
@@ -4296,7 +4296,7 @@
         <v>1.07</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,16 +4382,16 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="O25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P25" t="n">
         <v>4.15</v>
       </c>
-      <c r="P25" t="n">
-        <v>4.45</v>
-      </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R25" t="n">
         <v>2.39</v>
@@ -4400,7 +4400,7 @@
         <v>1.24</v>
       </c>
       <c r="T25" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U25" t="n">
         <v>2.26</v>
@@ -4409,22 +4409,22 @@
         <v>1.56</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z25" t="n">
         <v>4.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC25" t="n">
         <v>2.39</v>
@@ -4433,13 +4433,13 @@
         <v>1.57</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF25" t="n">
         <v>1.56</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>7.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="R26" t="n">
         <v>2.4</v>
@@ -4559,31 +4559,31 @@
         <v>1.26</v>
       </c>
       <c r="T26" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U26" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="V26" t="n">
         <v>1.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
         <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z26" t="n">
         <v>4.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="AC26" t="n">
         <v>2.63</v>
@@ -4592,13 +4592,13 @@
         <v>1.41</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF26" t="n">
         <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4709,22 +4709,22 @@
         <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="R27" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T27" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="V27" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W27" t="n">
         <v>1.09</v>
@@ -4733,10 +4733,10 @@
         <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
       <c r="AA27" t="n">
         <v>1.72</v>
@@ -4757,7 +4757,7 @@
         <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="AK27" t="n">
         <v>1.53</v>
@@ -4868,7 +4868,7 @@
         <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="R28" t="n">
         <v>2.2</v>
@@ -4880,7 +4880,7 @@
         <v>2.92</v>
       </c>
       <c r="U28" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V28" t="n">
         <v>1.4</v>
@@ -4892,7 +4892,7 @@
         <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
         <v>3.55</v>
@@ -4907,16 +4907,16 @@
         <v>2.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AK28" t="n">
         <v>1.4</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.85</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="S7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.18</v>
       </c>
-      <c r="T7" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.15</v>
-      </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AB7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.69</v>
       </c>
-      <c r="AC7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="P8" t="n">
-        <v>4.33</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.11</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="S8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T8" t="n">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="U8" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.75</v>
+        <v>5.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.84</v>
+        <v>1.77</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.15</v>
+        <v>3.42</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T9" t="n">
         <v>4.4</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.88</v>
-      </c>
       <c r="U9" t="n">
-        <v>2.6</v>
+        <v>1.84</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.48</v>
+        <v>6.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AB9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC9" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC9" t="n">
-        <v>2.97</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.88</v>
+        <v>2.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>2.15</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>4.85</v>
       </c>
       <c r="R10" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="S10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T10" t="n">
         <v>3.82</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.95</v>
+        <v>5.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.84</v>
+        <v>1.48</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.77</v>
+        <v>2.45</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.42</v>
+        <v>1.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
         <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>1.61</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.75</v>
+        <v>5.24</v>
       </c>
       <c r="R11" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="S11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.22</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Z11" t="n">
-        <v>5.4</v>
+        <v>3.48</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.19</v>
+        <v>2.97</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.69</v>
+        <v>1.88</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.51</v>
+        <v>1.11</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>2.23</v>
+        <v>4.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.14</v>
+        <v>2.2</v>
       </c>
       <c r="R12" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="V12" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.22</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1.43</v>
+        <v>2.05</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P13" t="n">
-        <v>4.2</v>
+        <v>2.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.2</v>
+        <v>3.14</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="U13" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.33</v>
+        <v>6.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.51</v>
+        <v>1.82</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.13</v>
+        <v>3.27</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.05</v>
+        <v>1.43</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.48</v>
+        <v>5.35</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P16" t="n">
         <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="R16" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T16" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
         <v>1.72</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.11</v>
+        <v>1.72</v>
       </c>
       <c r="O17" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>3.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.56</v>
+        <v>2.2</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
         <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="U17" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.99</v>
+        <v>4.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.2</v>
+        <v>1.82</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>6.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.69</v>
+        <v>2.62</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.72</v>
+        <v>4.11</v>
       </c>
       <c r="O20" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P20" t="n">
-        <v>3.55</v>
+        <v>1.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>4.56</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S20" t="n">
         <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="U20" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.33</v>
+        <v>3.99</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.82</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z21" t="n">
         <v>4.2</v>
       </c>
-      <c r="P21" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AA21" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.62</v>
+        <v>1.69</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>2.48</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>5.35</v>
+        <v>4.5</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="R23" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T23" t="n">
-        <v>3.11</v>
+        <v>2.91</v>
       </c>
       <c r="U23" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W23" t="n">
         <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AB23" t="n">
         <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
         <v>1.08</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>2.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>2.11</v>
       </c>
       <c r="R7" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.22</v>
       </c>
-      <c r="T7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.18</v>
-      </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.4</v>
+        <v>6.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.51</v>
+        <v>2.15</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>4.33</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.11</v>
+        <v>4.85</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="S9" t="n">
         <v>1.18</v>
       </c>
       <c r="T9" t="n">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.75</v>
+        <v>5.7</v>
       </c>
       <c r="AA9" t="n">
         <v>1.36</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.84</v>
+        <v>2.45</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.15</v>
+        <v>1.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.85</v>
+        <v>5.24</v>
       </c>
       <c r="R10" t="n">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>3.82</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="V10" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.08</v>
       </c>
-      <c r="Z10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.45</v>
+        <v>1.88</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
         <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.61</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.24</v>
+        <v>2.75</v>
       </c>
       <c r="R11" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.48</v>
+        <v>5.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.97</v>
+        <v>2.19</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.79</v>
+        <v>1.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.88</v>
+        <v>2.69</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P12" t="n">
-        <v>4.2</v>
+        <v>2.23</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>3.14</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="U12" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.33</v>
+        <v>6.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.51</v>
+        <v>1.82</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.13</v>
+        <v>3.27</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.05</v>
+        <v>1.43</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O13" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.23</v>
+        <v>4.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.14</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.22</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.43</v>
+        <v>2.05</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.7</v>
+        <v>1.72</v>
       </c>
       <c r="O16" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>3.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U16" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="V16" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>2.05</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.2</v>
+        <v>1.82</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.72</v>
+        <v>4.11</v>
       </c>
       <c r="O17" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P17" t="n">
-        <v>3.55</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>4.56</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
         <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="U17" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.33</v>
+        <v>3.99</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.82</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>6.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.91</v>
+        <v>4.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="U18" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.62</v>
+        <v>1.17</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="O19" t="n">
-        <v>4.65</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>6.54</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U19" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="V19" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.82</v>
+        <v>2.32</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.48</v>
+        <v>1.69</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.11</v>
+        <v>2.48</v>
       </c>
       <c r="O20" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q20" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>6.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U21" t="n">
         <v>2.3</v>
       </c>
-      <c r="S21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.46</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.32</v>
+        <v>1.82</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.48</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z23" t="n">
         <v>4.5</v>
       </c>
-      <c r="O23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="AA23" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.17</v>
+        <v>2.62</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -884,25 +884,25 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="O3" t="n">
-        <v>3.71</v>
+        <v>3.55</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>2.32</v>
       </c>
       <c r="Q3" t="n">
         <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T3" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="U3" t="n">
         <v>2.2</v>
@@ -914,28 +914,28 @@
         <v>1.17</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>5.24</v>
       </c>
       <c r="AA3" t="n">
         <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF3" t="n">
         <v>1.42</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="O6" t="n">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>4.84</v>
+        <v>4.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
         <v>1.42</v>
@@ -1391,28 +1391,28 @@
         <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
         <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="n">
         <v>2.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.48</v>
+        <v>4.1</v>
       </c>
       <c r="AD6" t="n">
         <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF6" t="n">
         <v>1.9</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>4.33</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.11</v>
+        <v>5.24</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="U7" t="n">
-        <v>1.84</v>
+        <v>2.6</v>
       </c>
       <c r="V7" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.75</v>
+        <v>3.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.25</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.85</v>
+        <v>2.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.84</v>
+        <v>1.89</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.15</v>
+        <v>1.11</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="O8" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="R8" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="S8" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T8" t="n">
-        <v>3.82</v>
+        <v>4.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="V8" t="n">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.95</v>
+        <v>7.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.77</v>
+        <v>2.88</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.42</v>
+        <v>2.15</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1844,19 +1844,19 @@
         <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="R9" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="S9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="U9" t="n">
         <v>2.1</v>
@@ -1865,22 +1865,22 @@
         <v>1.67</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AC9" t="n">
         <v>1.98</v>
@@ -1892,10 +1892,10 @@
         <v>1.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>2.35</v>
       </c>
       <c r="O10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.6</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.88</v>
-      </c>
       <c r="U10" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.88</v>
+        <v>2.69</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="S11" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="U11" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
         <v>5.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.44</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.69</v>
+        <v>1.99</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.51</v>
+        <v>3.42</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P12" t="n">
         <v>3.9</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.23</v>
-      </c>
       <c r="Q12" t="n">
-        <v>3.14</v>
+        <v>2.2</v>
       </c>
       <c r="R12" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.17</v>
       </c>
-      <c r="T12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1.43</v>
+        <v>2.05</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="O13" t="n">
         <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>4.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.2</v>
+        <v>3.14</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.3</v>
       </c>
-      <c r="T13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AG13" t="n">
-        <v>2.13</v>
+        <v>3.25</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.05</v>
+        <v>1.43</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5.35</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T15" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
         <v>3.62</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>2.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.72</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.95</v>
+        <v>3.62</v>
       </c>
       <c r="P16" t="n">
-        <v>3.55</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="U16" t="n">
-        <v>2.39</v>
+        <v>2.67</v>
       </c>
       <c r="V16" t="n">
         <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="AA16" t="n">
         <v>1.76</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.46</v>
+        <v>2.95</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.82</v>
+        <v>1.13</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.11</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.8</v>
+        <v>4.65</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>6.54</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.56</v>
+        <v>1.82</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="U17" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="V17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.44</v>
       </c>
-      <c r="W17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.2</v>
+        <v>2.48</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>1.99</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="R18" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.91</v>
+        <v>3.6</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.83</v>
+        <v>2.51</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.1</v>
+        <v>5.35</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>3.11</v>
       </c>
       <c r="U19" t="n">
-        <v>2.46</v>
+        <v>2.65</v>
       </c>
       <c r="V19" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.51</v>
+        <v>2.89</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE19" t="n">
         <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.32</v>
+        <v>1.75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.69</v>
+        <v>1.13</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.48</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.7</v>
+        <v>4.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="O21" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="P21" t="n">
-        <v>6.54</v>
+        <v>6.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="R21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U21" t="n">
         <v>2.4</v>
       </c>
-      <c r="S21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.3</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="W21" t="n">
         <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
         <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.1</v>
+        <v>4.56</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="V22" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.4</v>
+        <v>3.99</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
         <v>1.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>2.05</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
         <v>1.2</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK23" t="n">
         <v>1.44</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P23" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>2.62</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4229,7 +4229,7 @@
         <v>3.95</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
         <v>2.71</v>
@@ -4247,10 +4247,10 @@
         <v>1.85</v>
       </c>
       <c r="V24" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -4265,7 +4265,7 @@
         <v>1.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AC24" t="n">
         <v>1.78</v>
@@ -4277,7 +4277,7 @@
         <v>1.39</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AG24" t="n">
         <v>3.34</v>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,16 +4382,16 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="O25" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P25" t="n">
         <v>4.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
         <v>2.39</v>
@@ -4409,7 +4409,7 @@
         <v>1.56</v>
       </c>
       <c r="W25" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK25" t="n">
         <v>2.12</v>
@@ -4565,7 +4565,7 @@
         <v>2.52</v>
       </c>
       <c r="V26" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W26" t="n">
         <v>1.06</v>
@@ -4589,7 +4589,7 @@
         <v>2.63</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE26" t="n">
         <v>1.13</v>
@@ -4598,7 +4598,7 @@
         <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4709,25 +4709,25 @@
         <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="R27" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S27" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T27" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="U27" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="V27" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
         <v>1.03</v>
@@ -4754,7 +4754,7 @@
         <v>1.11</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG27" t="n">
         <v>2.18</v>
@@ -4773,7 +4773,7 @@
         <v>1.48</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4868,7 +4868,7 @@
         <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="R28" t="n">
         <v>2.2</v>
@@ -4892,22 +4892,22 @@
         <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z28" t="n">
         <v>3.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE28" t="n">
         <v>1.11</v>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.61</v>
+        <v>8</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.24</v>
+        <v>1.65</v>
       </c>
       <c r="R7" t="n">
-        <v>2.18</v>
+        <v>2.64</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88</v>
+        <v>3.82</v>
       </c>
       <c r="U7" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.48</v>
+        <v>5.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.95</v>
+        <v>1.96</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.74</v>
       </c>
       <c r="AE7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.08</v>
       </c>
-      <c r="AF7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.11</v>
+        <v>3.42</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.61</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>4.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="W8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.22</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T9" t="n">
         <v>4.6</v>
       </c>
-      <c r="O9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.72</v>
-      </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="V9" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AB9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.88</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.48</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.35</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.45</v>
+        <v>1.61</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.8</v>
+        <v>5.24</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.22</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Z10" t="n">
-        <v>5.4</v>
+        <v>3.48</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.46</v>
+        <v>1.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.19</v>
+        <v>2.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.69</v>
+        <v>1.89</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.52</v>
+        <v>1.11</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.65</v>
+        <v>4.95</v>
       </c>
       <c r="R11" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="S11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T11" t="n">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.84</v>
+        <v>1.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.99</v>
+        <v>2.48</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.42</v>
+        <v>1.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>4.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>2.64</v>
+        <v>2.39</v>
       </c>
       <c r="V15" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.62</v>
+        <v>4.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.13</v>
+        <v>1.92</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>5.35</v>
       </c>
       <c r="O16" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="S16" t="n">
         <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="U16" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
         <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
         <v>1.13</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O17" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="P17" t="n">
-        <v>6.54</v>
+        <v>6.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T17" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
         <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.99</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.51</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.69</v>
+        <v>1.13</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5.35</v>
+        <v>1.4</v>
       </c>
       <c r="O19" t="n">
-        <v>3.8</v>
+        <v>4.65</v>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>6.54</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>1.82</v>
       </c>
       <c r="R19" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>3.11</v>
+        <v>3.22</v>
       </c>
       <c r="U19" t="n">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.62</v>
+        <v>4.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
         <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.13</v>
+        <v>2.48</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>2.41</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>3.06</v>
       </c>
       <c r="P20" t="n">
-        <v>4.46</v>
+        <v>2.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="S20" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="T20" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="U20" t="n">
-        <v>2.39</v>
+        <v>2.96</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.35</v>
+        <v>2.92</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.46</v>
+        <v>3.58</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.92</v>
+        <v>1.44</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.44</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>4.55</v>
+        <v>3.62</v>
       </c>
       <c r="P21" t="n">
-        <v>6.25</v>
+        <v>1.66</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.91</v>
+        <v>4.8</v>
       </c>
       <c r="R21" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="S21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="U21" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="V21" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK21" t="n">
-        <v>2.64</v>
+        <v>1.13</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.41</v>
+        <v>1.99</v>
       </c>
       <c r="O23" t="n">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3.12</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="S23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.42</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>5.25</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z7" t="n">
         <v>5.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.96</v>
+        <v>2.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>1.42</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.99</v>
+        <v>2.69</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.42</v>
+        <v>1.52</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.45</v>
+        <v>1.61</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>5.24</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.22</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Z8" t="n">
-        <v>5.4</v>
+        <v>3.48</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.46</v>
+        <v>1.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.19</v>
+        <v>2.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.69</v>
+        <v>1.89</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.52</v>
+        <v>1.11</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.09</v>
+        <v>4.95</v>
       </c>
       <c r="R9" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="S9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>4.6</v>
+        <v>3.72</v>
       </c>
       <c r="U9" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.15</v>
+        <v>1.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.61</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.24</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>2.18</v>
+        <v>2.64</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>3.82</v>
       </c>
       <c r="U10" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.48</v>
+        <v>5.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.95</v>
+        <v>1.96</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.74</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.08</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.11</v>
+        <v>3.42</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T11" t="n">
         <v>4.6</v>
       </c>
-      <c r="O11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.72</v>
-      </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="V11" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AB11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2.88</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.48</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>1.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,52 +2792,52 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="P15" t="n">
-        <v>4.46</v>
+        <v>6.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S15" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AD15" t="n">
         <v>1.43</v>
@@ -2846,10 +2846,10 @@
         <v>1.14</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.92</v>
+        <v>2.64</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.35</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>1.57</v>
+        <v>4.46</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T16" t="n">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.62</v>
+        <v>4.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.89</v>
+        <v>2.46</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.13</v>
+        <v>1.92</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.44</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>4.55</v>
+        <v>3.85</v>
       </c>
       <c r="P17" t="n">
-        <v>6.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>4.56</v>
       </c>
       <c r="R17" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="V17" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.64</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z18" t="n">
         <v>4.2</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="AA18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB18" t="n">
         <v>2.2</v>
       </c>
-      <c r="S18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2</v>
-      </c>
       <c r="AC18" t="n">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>5.35</v>
       </c>
       <c r="O21" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="P21" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="S21" t="n">
         <v>1.33</v>
       </c>
       <c r="T21" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="U21" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="V21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
         <v>1.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK21" t="n">
         <v>1.13</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P22" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.56</v>
+        <v>5.1</v>
       </c>
       <c r="R22" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U22" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.99</v>
+        <v>3.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE22" t="n">
         <v>1.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.99</v>
+        <v>4.5</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S23" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T23" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="U23" t="n">
-        <v>2.39</v>
+        <v>2.67</v>
       </c>
       <c r="V23" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.51</v>
+        <v>2.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK23" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.69</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T9" t="n">
         <v>4.6</v>
       </c>
-      <c r="O9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.72</v>
-      </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="V9" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AB9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.88</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.48</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>1.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>4.95</v>
       </c>
       <c r="R10" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="S10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T10" t="n">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.84</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.99</v>
+        <v>2.48</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.42</v>
+        <v>1.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="P11" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.09</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T11" t="n">
-        <v>4.6</v>
+        <v>3.82</v>
       </c>
       <c r="U11" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="W11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.88</v>
+        <v>1.99</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.15</v>
+        <v>3.42</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="O12" t="n">
         <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>3.14</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S12" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="U12" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.33</v>
+        <v>6.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>3.09</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.51</v>
+        <v>1.82</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.13</v>
+        <v>3.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.05</v>
+        <v>1.43</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.62</v>
+        <v>1.67</v>
       </c>
       <c r="O13" t="n">
         <v>3.7</v>
       </c>
       <c r="P13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB13" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="AC13" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.17</v>
       </c>
-      <c r="T13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.43</v>
+        <v>2.05</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.44</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>4.55</v>
+        <v>3.62</v>
       </c>
       <c r="P15" t="n">
-        <v>6.25</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.91</v>
+        <v>4.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="S15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="V15" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK15" t="n">
-        <v>2.64</v>
+        <v>1.13</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,52 +2951,52 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="P16" t="n">
-        <v>4.46</v>
+        <v>6.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S16" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AD16" t="n">
         <v>1.43</v>
@@ -3005,10 +3005,10 @@
         <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.92</v>
+        <v>2.64</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="O17" t="n">
         <v>3.8</v>
       </c>
-      <c r="O17" t="n">
-        <v>3.85</v>
-      </c>
       <c r="P17" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.56</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="U17" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.99</v>
+        <v>3.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.99</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.51</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.69</v>
+        <v>1.13</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="O19" t="n">
-        <v>4.65</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>6.54</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="R19" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="U19" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE19" t="n">
         <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.48</v>
+        <v>1.69</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.41</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>3.06</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.7</v>
+        <v>4.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="T20" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
-        <v>2.96</v>
+        <v>2.39</v>
       </c>
       <c r="V20" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.92</v>
+        <v>4.35</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.58</v>
+        <v>2.46</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.44</v>
+        <v>1.92</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>5.35</v>
+        <v>2.41</v>
       </c>
       <c r="O21" t="n">
-        <v>3.8</v>
+        <v>3.06</v>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>3.12</v>
       </c>
       <c r="R21" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T21" t="n">
-        <v>3.11</v>
+        <v>2.56</v>
       </c>
       <c r="U21" t="n">
-        <v>2.65</v>
+        <v>2.96</v>
       </c>
       <c r="V21" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z21" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.1</v>
+        <v>4.56</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="V22" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.62</v>
+        <v>3.99</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
         <v>1.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="O23" t="n">
-        <v>3.62</v>
+        <v>4.65</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>6.54</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.8</v>
+        <v>1.82</v>
       </c>
       <c r="R23" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="S23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T23" t="n">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="U23" t="n">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.13</v>
+        <v>2.48</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
         <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="R3" t="n">
         <v>2.4</v>
@@ -905,22 +905,22 @@
         <v>3.44</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V3" t="n">
         <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
         <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.24</v>
+        <v>7.28</v>
       </c>
       <c r="AA3" t="n">
         <v>1.5</v>
@@ -929,19 +929,19 @@
         <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF3" t="n">
         <v>1.42</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1361,55 +1361,55 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="O6" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z6" t="n">
         <v>3.35</v>
       </c>
-      <c r="P6" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AA6" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE6" t="n">
         <v>1.07</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R7" t="n">
         <v>2.35</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.3</v>
       </c>
       <c r="S7" t="n">
         <v>1.22</v>
@@ -1541,7 +1541,7 @@
         <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.64</v>
@@ -1553,31 +1553,31 @@
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE7" t="n">
         <v>1.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1709,7 +1709,7 @@
         <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
         <v>1.22</v>
@@ -1724,7 +1724,7 @@
         <v>1.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AD8" t="n">
         <v>1.3</v>
@@ -1733,10 +1733,10 @@
         <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>5.16</v>
       </c>
       <c r="O9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="P9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.17</v>
       </c>
-      <c r="T9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.15</v>
+        <v>1.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="O10" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T10" t="n">
         <v>4.2</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.72</v>
-      </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="V10" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.38</v>
       </c>
-      <c r="AB10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.48</v>
+        <v>2.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="R11" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>3.82</v>
+        <v>3.96</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V11" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF11" t="n">
         <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.42</v>
+        <v>4.25</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="S12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T12" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="W12" t="n">
         <v>1.22</v>
@@ -2351,28 +2351,28 @@
         <v>1.04</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.85</v>
+        <v>6.8</v>
       </c>
       <c r="AA12" t="n">
         <v>1.36</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF12" t="n">
         <v>1.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="P13" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S13" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T13" t="n">
         <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V13" t="n">
         <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
         <v>4.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB13" t="n">
         <v>2.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>3.62</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF14" t="n">
         <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="O15" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.8</v>
+        <v>3.12</v>
       </c>
       <c r="R15" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
-        <v>3.17</v>
+        <v>2.56</v>
       </c>
       <c r="U15" t="n">
-        <v>2.67</v>
+        <v>2.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>4.55</v>
+        <v>3.62</v>
       </c>
       <c r="P16" t="n">
-        <v>6.25</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.91</v>
+        <v>5.16</v>
       </c>
       <c r="R16" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="S16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
         <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.48</v>
+        <v>2.94</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.64</v>
+        <v>1.13</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5.35</v>
+        <v>2.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.57</v>
+        <v>2.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>2.52</v>
       </c>
       <c r="R17" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>3.11</v>
+        <v>3.6</v>
       </c>
       <c r="U17" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="V17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.42</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.32</v>
       </c>
       <c r="AE17" t="n">
         <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>5.35</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.1</v>
+        <v>5.66</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="U18" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="V18" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z18" t="n">
         <v>3.62</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
         <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK18" t="n">
         <v>1.13</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.99</v>
+        <v>1.44</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
         <v>3.6</v>
       </c>
       <c r="U19" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="V19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>4.41</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.69</v>
+        <v>2.64</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P20" t="n">
         <v>1.7</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P20" t="n">
-        <v>4.46</v>
-      </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>4.56</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S20" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U20" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.35</v>
+        <v>3.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.46</v>
+        <v>2.81</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.92</v>
+        <v>1.16</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.41</v>
+        <v>1.64</v>
       </c>
       <c r="O21" t="n">
-        <v>3.06</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="R21" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="S21" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="T21" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
         <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.58</v>
+        <v>2.52</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>4.51</v>
       </c>
       <c r="O22" t="n">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="P22" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.56</v>
+        <v>5.02</v>
       </c>
       <c r="R22" t="n">
         <v>2.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="U22" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.99</v>
+        <v>3.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK22" t="n">
         <v>1.2</v>
@@ -4067,16 +4067,16 @@
         <v>1.4</v>
       </c>
       <c r="O23" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="P23" t="n">
-        <v>6.54</v>
+        <v>6.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="R23" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S23" t="n">
         <v>1.3</v>
@@ -4085,7 +4085,7 @@
         <v>3.22</v>
       </c>
       <c r="U23" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="V23" t="n">
         <v>1.5</v>
@@ -4094,13 +4094,13 @@
         <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA23" t="n">
         <v>1.63</v>
@@ -4109,19 +4109,19 @@
         <v>2.35</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD23" t="n">
         <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
         <v>2.48</v>
@@ -4223,22 +4223,22 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="O24" t="n">
-        <v>3.95</v>
+        <v>3.87</v>
       </c>
       <c r="P24" t="n">
-        <v>2.54</v>
+        <v>2.28</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="R24" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T24" t="n">
         <v>4.35</v>
@@ -4247,10 +4247,10 @@
         <v>1.85</v>
       </c>
       <c r="V24" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -4271,10 +4271,10 @@
         <v>1.78</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AF24" t="n">
         <v>1.2</v>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,22 +4382,22 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="O25" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P25" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="R25" t="n">
         <v>2.39</v>
       </c>
       <c r="S25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T25" t="n">
         <v>3.34</v>
@@ -4427,19 +4427,19 @@
         <v>2.35</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE25" t="n">
         <v>1.18</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4550,22 +4550,22 @@
         <v>7.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="R26" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S26" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T26" t="n">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="U26" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="V26" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W26" t="n">
         <v>1.06</v>
@@ -4577,28 +4577,28 @@
         <v>1.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4709,49 +4709,49 @@
         <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="S27" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T27" t="n">
-        <v>2.63</v>
+        <v>3.08</v>
       </c>
       <c r="U27" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
         <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z27" t="n">
         <v>3.84</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF27" t="n">
         <v>1.58</v>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>2.92</v>
       </c>
       <c r="U28" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V28" t="n">
         <v>1.4</v>
@@ -4892,31 +4892,31 @@
         <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="AA28" t="n">
         <v>1.63</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AC28" t="n">
         <v>2.97</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AK28" t="n">
         <v>1.43</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU28"/>
+  <dimension ref="A1:AU29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.52</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.37</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.12</v>
+        <v>5.24</v>
       </c>
       <c r="R7" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="S7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.22</v>
       </c>
-      <c r="T7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>3.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.44</v>
+        <v>1.81</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.43</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>2.52</v>
       </c>
       <c r="O8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T8" t="n">
         <v>3.6</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.88</v>
-      </c>
       <c r="U8" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z8" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.88</v>
+        <v>2.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5.16</v>
+        <v>1.2</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.53</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.13</v>
+        <v>1.54</v>
       </c>
       <c r="R9" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="V9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.1</v>
+        <v>4.25</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>5.16</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.54</v>
+        <v>5.13</v>
       </c>
       <c r="R11" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="S11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.17</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.16</v>
-      </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.1</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>4.25</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.31</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="S12" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="T12" t="n">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>2.41</v>
       </c>
       <c r="V12" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>2.31</v>
       </c>
       <c r="O13" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>4.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S13" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="T13" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB13" t="n">
         <v>3.1</v>
       </c>
-      <c r="U13" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AC13" t="n">
-        <v>2.48</v>
+        <v>1.89</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.1</v>
+        <v>1.41</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.37</v>
+        <v>1.64</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="S15" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="T15" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.58</v>
+        <v>2.52</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.62</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>6.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.16</v>
+        <v>1.94</v>
       </c>
       <c r="R16" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.91</v>
+        <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.13</v>
+        <v>2.48</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.1</v>
+        <v>5.35</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.87</v>
+        <v>1.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.52</v>
+        <v>5.66</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>3.6</v>
+        <v>3.11</v>
       </c>
       <c r="U17" t="n">
-        <v>2.39</v>
+        <v>2.65</v>
       </c>
       <c r="V17" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.51</v>
+        <v>2.89</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE17" t="n">
         <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.69</v>
+        <v>1.13</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,61 +3269,61 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5.35</v>
+        <v>2.37</v>
       </c>
       <c r="O18" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.57</v>
+        <v>2.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.66</v>
+        <v>3.12</v>
       </c>
       <c r="R18" t="n">
-        <v>2.19</v>
+        <v>1.97</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T18" t="n">
-        <v>3.11</v>
+        <v>2.56</v>
       </c>
       <c r="U18" t="n">
-        <v>2.65</v>
+        <v>2.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z18" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AE18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.79</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
         <v>1.9</v>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.44</v>
+        <v>4.51</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="P19" t="n">
-        <v>5.5</v>
+        <v>1.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.97</v>
+        <v>5.02</v>
       </c>
       <c r="R19" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="U19" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="V19" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="W19" t="n">
         <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.41</v>
+        <v>3.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.64</v>
+        <v>1.2</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.92</v>
+        <v>1.44</v>
       </c>
       <c r="O20" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.56</v>
+        <v>1.97</v>
       </c>
       <c r="R20" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
         <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.95</v>
+        <v>4.41</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.16</v>
+        <v>2.64</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.64</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
         <v>3.7</v>
       </c>
-      <c r="P21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AA21" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.52</v>
+        <v>2.94</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK21" t="n">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.51</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.02</v>
+        <v>4.56</v>
       </c>
       <c r="R22" t="n">
         <v>2.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.62</v>
+        <v>3.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>6.12</v>
+        <v>2.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.94</v>
+        <v>2.52</v>
       </c>
       <c r="R23" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T23" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="U23" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V23" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.48</v>
+        <v>1.69</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>3.87</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.28</v>
+        <v>2.59</v>
       </c>
       <c r="Q24" t="n">
         <v>2.65</v>
@@ -4271,10 +4271,10 @@
         <v>1.78</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AF24" t="n">
         <v>1.2</v>
@@ -4296,7 +4296,7 @@
         <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4653,12 +4653,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,84 +4696,84 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.25</v>
+        <v>1.24</v>
       </c>
       <c r="O27" t="n">
+        <v>5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T27" t="n">
         <v>3.4</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.08</v>
-      </c>
       <c r="U27" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="V27" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.09</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK27" t="n">
-        <v>1.5</v>
+        <v>3.45</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="AU27" s="3" t="n">
-        <v>46206.9375</v>
+        <v>46206.875</v>
       </c>
     </row>
     <row r="28">
@@ -4812,156 +4812,315 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Denver Summit W</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" s="3" t="n">
+        <v>46206.9375</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N28" t="n">
+      <c r="N29" t="n">
         <v>2.6</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O29" t="n">
         <v>3.1</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P29" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q29" t="n">
         <v>2.88</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R29" t="n">
         <v>2.2</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S29" t="n">
         <v>1.32</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T29" t="n">
         <v>2.92</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U29" t="n">
         <v>2.56</v>
       </c>
-      <c r="V28" t="n">
+      <c r="V29" t="n">
         <v>1.4</v>
       </c>
-      <c r="W28" t="n">
+      <c r="W29" t="n">
         <v>1.08</v>
       </c>
-      <c r="X28" t="n">
+      <c r="X29" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Y29" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="Z29" t="n">
         <v>2.8</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AA29" t="n">
         <v>1.63</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AB29" t="n">
         <v>1.89</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AC29" t="n">
         <v>2.97</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AD29" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AE29" t="n">
         <v>1.07</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AF29" t="n">
         <v>1.5</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AG29" t="n">
         <v>1.87</v>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28" t="n">
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.24</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AK29" t="n">
         <v>1.43</v>
       </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" s="3" t="n">
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" s="3" t="n">
         <v>46206.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>5.16</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.24</v>
+        <v>5.13</v>
       </c>
       <c r="R7" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.48</v>
+        <v>5.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.52</v>
+        <v>1.2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.37</v>
+        <v>11</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.12</v>
+        <v>1.54</v>
       </c>
       <c r="R8" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>3.96</v>
       </c>
       <c r="U8" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="V8" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>1.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.7</v>
+        <v>1.77</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.47</v>
+        <v>4.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
+        <v>1.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.54</v>
+        <v>5.24</v>
       </c>
       <c r="R9" t="n">
-        <v>3.2</v>
+        <v>2.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>3.96</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.5</v>
+        <v>3.48</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.33</v>
+        <v>1.81</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>4.25</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.16</v>
+        <v>2.52</v>
       </c>
       <c r="O11" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.53</v>
+        <v>2.37</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.13</v>
+        <v>3.12</v>
       </c>
       <c r="R11" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="S11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>2.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>4.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S12" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="T12" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB12" t="n">
         <v>3.1</v>
       </c>
-      <c r="U12" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AC12" t="n">
-        <v>2.48</v>
+        <v>1.89</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.1</v>
+        <v>1.41</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.31</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R13" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="S13" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="T13" t="n">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.94</v>
+        <v>2.41</v>
       </c>
       <c r="V13" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.64</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
         <v>3.7</v>
       </c>
-      <c r="P15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AA15" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.52</v>
+        <v>2.94</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,61 +2951,61 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>2.37</v>
       </c>
       <c r="O16" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>6.12</v>
+        <v>2.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.94</v>
+        <v>3.12</v>
       </c>
       <c r="R16" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T16" t="n">
-        <v>3.22</v>
+        <v>2.56</v>
       </c>
       <c r="U16" t="n">
-        <v>2.41</v>
+        <v>2.96</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.3</v>
+        <v>2.92</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>2.06</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.62</v>
+        <v>3.58</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG16" t="n">
         <v>1.9</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5.35</v>
+        <v>3.92</v>
       </c>
       <c r="O17" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="P17" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.66</v>
+        <v>4.56</v>
       </c>
       <c r="R17" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="U17" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.62</v>
+        <v>3.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.37</v>
+        <v>1.64</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="R18" t="n">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="S18" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="T18" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.58</v>
+        <v>2.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,34 +3428,34 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.51</v>
+        <v>5.35</v>
       </c>
       <c r="O19" t="n">
-        <v>3.68</v>
+        <v>4.1</v>
       </c>
       <c r="P19" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.02</v>
+        <v>5.66</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="U19" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="V19" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
@@ -3467,25 +3467,25 @@
         <v>3.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P20" t="n">
-        <v>5.5</v>
+        <v>6.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="R20" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S20" t="n">
         <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U20" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="V20" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.11</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AK20" t="n">
         <v>2.48</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.64</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="O21" t="n">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="P21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1.66</v>
       </c>
-      <c r="Q21" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.94</v>
+        <v>2.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.13</v>
+        <v>2.64</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>4.51</v>
       </c>
       <c r="O22" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.56</v>
+        <v>5.02</v>
       </c>
       <c r="R22" t="n">
         <v>2.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="U22" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>3.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,69 +4537,69 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O26" t="n">
         <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="R26" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S26" t="n">
         <v>1.27</v>
       </c>
       <c r="T26" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="U26" t="n">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="V26" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.64</v>
       </c>
-      <c r="AB26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O27" t="n">
         <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="R27" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S27" t="n">
         <v>1.27</v>
       </c>
       <c r="T27" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="U27" t="n">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="V27" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK27" t="n">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.16</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.13</v>
+        <v>5.24</v>
       </c>
       <c r="R7" t="n">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="V7" t="n">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.4</v>
+        <v>3.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="O8" t="n">
-        <v>5.5</v>
+        <v>4.15</v>
       </c>
       <c r="P8" t="n">
-        <v>11</v>
+        <v>3.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.54</v>
+        <v>2.07</v>
       </c>
       <c r="R8" t="n">
-        <v>3.2</v>
+        <v>2.52</v>
       </c>
       <c r="S8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T8" t="n">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="V8" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.77</v>
+        <v>2.93</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AK8" t="n">
-        <v>4.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.61</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.24</v>
+        <v>1.54</v>
       </c>
       <c r="R9" t="n">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="S9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA9" t="n">
         <v>1.33</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AB9" t="n">
-        <v>1.88</v>
+        <v>2.83</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>4.25</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.5</v>
       </c>
-      <c r="O10" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AB10" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>4.51</v>
       </c>
       <c r="O15" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z15" t="n">
         <v>3.62</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AA15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AB15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG15" t="n">
         <v>2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.98</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.37</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="P16" t="n">
-        <v>2.62</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.12</v>
+        <v>5.16</v>
       </c>
       <c r="R16" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="S16" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>2.56</v>
+        <v>2.91</v>
       </c>
       <c r="U16" t="n">
-        <v>2.96</v>
+        <v>2.67</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.92</v>
+        <v>3.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.58</v>
+        <v>2.94</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.92</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>6.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.56</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V17" t="n">
         <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
         <v>1.15</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.16</v>
+        <v>2.48</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>3.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="R18" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U18" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="V18" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O20" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P20" t="n">
-        <v>6.12</v>
+        <v>5.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="R20" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S20" t="n">
         <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.3</v>
+        <v>4.41</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.44</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.64</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.51</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.02</v>
+        <v>4.56</v>
       </c>
       <c r="R22" t="n">
         <v>2.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.62</v>
+        <v>3.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.87</v>
+        <v>3.8</v>
       </c>
       <c r="Q23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.52</v>
       </c>
-      <c r="R23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.51</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O26" t="n">
         <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="R26" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S26" t="n">
         <v>1.27</v>
       </c>
       <c r="T26" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="U26" t="n">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="V26" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,69 +4696,69 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O27" t="n">
         <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="R27" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S27" t="n">
         <v>1.27</v>
       </c>
       <c r="T27" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="U27" t="n">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="V27" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.64</v>
       </c>
-      <c r="AB27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK27" t="n">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -887,25 +887,25 @@
         <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P3" t="n">
         <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.81</v>
+        <v>2.92</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="S3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
         <v>1.6</v>
@@ -917,31 +917,31 @@
         <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.28</v>
+        <v>5.57</v>
       </c>
       <c r="AA3" t="n">
         <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AF3" t="n">
         <v>1.42</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,25 +1043,25 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1073,34 +1073,34 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1364,28 +1364,28 @@
         <v>1.62</v>
       </c>
       <c r="O6" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>5.42</v>
+        <v>4.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="R6" t="n">
         <v>2.12</v>
       </c>
       <c r="S6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="U6" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
@@ -1394,31 +1394,31 @@
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
         <v>3.35</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.24</v>
+        <v>5.78</v>
       </c>
       <c r="R7" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
         <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="U7" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.11</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.5</v>
+        <v>2.52</v>
       </c>
       <c r="O8" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.73</v>
+        <v>2.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.07</v>
+        <v>3.12</v>
       </c>
       <c r="R8" t="n">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="S8" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="W8" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>5.16</v>
       </c>
       <c r="O9" t="n">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.54</v>
+        <v>5.13</v>
       </c>
       <c r="R9" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.1</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>4.25</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.16</v>
+        <v>1.5</v>
       </c>
       <c r="O10" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T10" t="n">
         <v>4.2</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.21</v>
       </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.17</v>
-      </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.52</v>
+        <v>1.17</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.37</v>
+        <v>11.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.12</v>
+        <v>1.54</v>
       </c>
       <c r="R11" t="n">
-        <v>2.35</v>
+        <v>3.25</v>
       </c>
       <c r="S11" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z11" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.43</v>
+        <v>3.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.7</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.47</v>
+        <v>4.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>2.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.16</v>
+        <v>2.52</v>
       </c>
       <c r="R16" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.91</v>
+        <v>3.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.94</v>
+        <v>2.51</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE16" t="n">
         <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,61 +3110,61 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>5.35</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="P17" t="n">
-        <v>6.12</v>
+        <v>1.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.94</v>
+        <v>5.66</v>
       </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="U17" t="n">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
         <v>1.9</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.48</v>
+        <v>1.13</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P18" t="n">
-        <v>2.87</v>
+        <v>1.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.52</v>
+        <v>5.16</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>3.6</v>
+        <v>2.91</v>
       </c>
       <c r="U18" t="n">
-        <v>2.39</v>
+        <v>2.67</v>
       </c>
       <c r="V18" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.51</v>
+        <v>2.94</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE18" t="n">
         <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.69</v>
+        <v>1.13</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,61 +3428,61 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5.35</v>
+        <v>1.4</v>
       </c>
       <c r="O19" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>6.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.66</v>
+        <v>1.94</v>
       </c>
       <c r="R19" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>3.11</v>
+        <v>3.22</v>
       </c>
       <c r="U19" t="n">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="V19" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
         <v>1.9</v>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.13</v>
+        <v>2.48</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.44</v>
+        <v>3.92</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="P20" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.97</v>
+        <v>4.56</v>
       </c>
       <c r="R20" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="U20" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
         <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.41</v>
+        <v>3.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.48</v>
+        <v>2.81</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.64</v>
+        <v>1.16</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.37</v>
+        <v>1.64</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="R21" t="n">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="S21" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="T21" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
         <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.58</v>
+        <v>2.52</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>1.44</v>
       </c>
       <c r="O22" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.56</v>
+        <v>1.97</v>
       </c>
       <c r="R22" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="U22" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
         <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>4.41</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.16</v>
+        <v>2.64</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.64</v>
+        <v>2.37</v>
       </c>
       <c r="O23" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.15</v>
+        <v>3.12</v>
       </c>
       <c r="R23" t="n">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="S23" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="T23" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="U23" t="n">
-        <v>2.36</v>
+        <v>2.96</v>
       </c>
       <c r="V23" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
         <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.4</v>
+        <v>2.92</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.66</v>
+        <v>2.06</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.52</v>
+        <v>3.58</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK23" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,25 +1043,25 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1073,34 +1073,34 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1232,34 +1232,34 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.52</v>
+        <v>1.5</v>
       </c>
       <c r="O8" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB8" t="n">
         <v>3.5</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W8" t="n">
+      <c r="AC8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.14</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.47</v>
+        <v>2.2</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5.16</v>
+        <v>1.17</v>
       </c>
       <c r="O9" t="n">
-        <v>4.25</v>
+        <v>6.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>11.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.13</v>
+        <v>1.54</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T9" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.48</v>
+        <v>1.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.5</v>
+        <v>5.16</v>
       </c>
       <c r="O10" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="P10" t="n">
-        <v>3.73</v>
+        <v>1.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.07</v>
+        <v>5.13</v>
       </c>
       <c r="R10" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="S10" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.78</v>
+        <v>2.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.93</v>
+        <v>2.48</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>11.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.54</v>
+        <v>3.02</v>
       </c>
       <c r="R11" t="n">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="V11" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.25</v>
+        <v>2.43</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>1.41</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.84</v>
+        <v>2.6</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.3</v>
+        <v>1.47</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="R12" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="S12" t="n">
         <v>1.16</v>
@@ -2336,10 +2336,10 @@
         <v>4.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="V12" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="W12" t="n">
         <v>1.22</v>
@@ -2348,31 +2348,31 @@
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AF12" t="n">
         <v>1.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="O13" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="P13" t="n">
-        <v>4.2</v>
+        <v>4.69</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R13" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S13" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T13" t="n">
         <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W13" t="n">
         <v>1.1</v>
@@ -2507,10 +2507,10 @@
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="AA13" t="n">
         <v>1.66</v>
@@ -2528,10 +2528,10 @@
         <v>1.14</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="V14" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
         <v>4.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
         <v>2.61</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF14" t="n">
         <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.51</v>
+        <v>2.46</v>
       </c>
       <c r="O15" t="n">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.02</v>
+        <v>2.91</v>
       </c>
       <c r="R15" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="U15" t="n">
-        <v>2.59</v>
+        <v>3.17</v>
       </c>
       <c r="V15" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.1</v>
+        <v>5.53</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.87</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.52</v>
+        <v>5.3</v>
       </c>
       <c r="R16" t="n">
         <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="V16" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.51</v>
+        <v>2.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.69</v>
+        <v>1.12</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5.35</v>
+        <v>1.72</v>
       </c>
       <c r="O17" t="n">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="P17" t="n">
-        <v>1.57</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.66</v>
+        <v>2.16</v>
       </c>
       <c r="R17" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="S17" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T17" t="n">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.13</v>
+        <v>2.02</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="O18" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.16</v>
+        <v>5.02</v>
       </c>
       <c r="R18" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="U18" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
         <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,31 +3428,31 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>3.76</v>
       </c>
       <c r="P19" t="n">
-        <v>6.12</v>
+        <v>2.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.94</v>
+        <v>2.52</v>
       </c>
       <c r="R19" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T19" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="U19" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
         <v>1.08</v>
@@ -3461,31 +3461,31 @@
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.3</v>
+        <v>4.54</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.48</v>
+        <v>1.69</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.92</v>
+        <v>1.39</v>
       </c>
       <c r="O20" t="n">
-        <v>3.74</v>
+        <v>4.3</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.56</v>
+        <v>1.97</v>
       </c>
       <c r="R20" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S20" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V20" t="n">
         <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.16</v>
+        <v>2.62</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="P21" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="R21" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="S21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="V21" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AD21" t="n">
         <v>1.47</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.44</v>
+        <v>4.52</v>
       </c>
       <c r="O22" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>5.5</v>
+        <v>1.66</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.97</v>
+        <v>4.4</v>
       </c>
       <c r="R22" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T22" t="n">
-        <v>3.6</v>
+        <v>2.91</v>
       </c>
       <c r="U22" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="V22" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.41</v>
+        <v>3.45</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.64</v>
+        <v>1.13</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.37</v>
+        <v>3.8</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="S23" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="U23" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.92</v>
+        <v>3.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.58</v>
+        <v>2.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.79</v>
+        <v>1.54</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4223,16 +4223,16 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P24" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="R24" t="n">
         <v>2.56</v>
@@ -4244,10 +4244,10 @@
         <v>4.35</v>
       </c>
       <c r="U24" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="V24" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="W24" t="n">
         <v>1.23</v>
@@ -4280,7 +4280,7 @@
         <v>1.2</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,16 +4382,16 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="P25" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="R25" t="n">
         <v>2.39</v>
@@ -4403,7 +4403,7 @@
         <v>3.34</v>
       </c>
       <c r="U25" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="V25" t="n">
         <v>1.56</v>
@@ -4415,22 +4415,22 @@
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z25" t="n">
         <v>4.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB25" t="n">
         <v>2.35</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE25" t="n">
         <v>1.18</v>
@@ -4439,7 +4439,7 @@
         <v>1.57</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK25" t="n">
         <v>2.12</v>
@@ -4550,25 +4550,25 @@
         <v>7.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="R26" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S26" t="n">
         <v>1.27</v>
       </c>
       <c r="T26" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="U26" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="V26" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
         <v>1.03</v>
@@ -4580,13 +4580,13 @@
         <v>4.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AD26" t="n">
         <v>1.4</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>5.85</v>
       </c>
       <c r="P27" t="n">
-        <v>8.9</v>
+        <v>11.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="R27" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S27" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T27" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="V27" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
         <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.04</v>
+        <v>3.13</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="AB27" t="n">
         <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AK27" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4877,7 +4877,7 @@
         <v>1.29</v>
       </c>
       <c r="T28" t="n">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="U28" t="n">
         <v>2.42</v>
@@ -4892,7 +4892,7 @@
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
         <v>3.84</v>
@@ -4913,7 +4913,7 @@
         <v>1.1</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG28" t="n">
         <v>2.18</v>
@@ -4932,7 +4932,7 @@
         <v>1.23</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5030,22 +5030,22 @@
         <v>2.88</v>
       </c>
       <c r="R29" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S29" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T29" t="n">
-        <v>2.92</v>
+        <v>3.07</v>
       </c>
       <c r="U29" t="n">
-        <v>2.56</v>
+        <v>2.13</v>
       </c>
       <c r="V29" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
         <v>1.05</v>
@@ -5054,13 +5054,13 @@
         <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA29" t="n">
         <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AC29" t="n">
         <v>2.97</v>
@@ -5072,10 +5072,10 @@
         <v>1.07</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>1.24</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>5.16</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.78</v>
+        <v>5.13</v>
       </c>
       <c r="R7" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>2.86</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.73</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>2.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.95</v>
+        <v>2.16</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.71</v>
+        <v>2.48</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>11.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.54</v>
+        <v>3.02</v>
       </c>
       <c r="R9" t="n">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="S9" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.25</v>
+        <v>2.43</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>1.41</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.84</v>
+        <v>2.6</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="AK9" t="n">
-        <v>4.3</v>
+        <v>1.47</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.16</v>
+        <v>1.17</v>
       </c>
       <c r="O10" t="n">
-        <v>4.25</v>
+        <v>6.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.47</v>
+        <v>11.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.13</v>
+        <v>1.54</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="V10" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.48</v>
+        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>1.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.02</v>
+        <v>5.78</v>
       </c>
       <c r="R11" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>2.86</v>
       </c>
       <c r="U11" t="n">
-        <v>2.16</v>
+        <v>2.73</v>
       </c>
       <c r="V11" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.43</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>2.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.46</v>
+        <v>1.39</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="P15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK15" t="n">
         <v>2.62</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.44</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.53</v>
+        <v>4.35</v>
       </c>
       <c r="O16" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.3</v>
+        <v>5.02</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="V16" t="n">
         <v>1.44</v>
       </c>
       <c r="W16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.05</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
         <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,43 +3110,43 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
         <v>3.76</v>
       </c>
       <c r="P17" t="n">
-        <v>4.4</v>
+        <v>2.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="R17" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U17" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V17" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>4.54</v>
       </c>
       <c r="AA17" t="n">
         <v>1.65</v>
@@ -3155,19 +3155,19 @@
         <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.35</v>
+        <v>1.41</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>5.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.02</v>
+        <v>1.94</v>
       </c>
       <c r="R18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB18" t="n">
         <v>2.25</v>
       </c>
-      <c r="S18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2</v>
-      </c>
       <c r="AC18" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.11</v>
       </c>
-      <c r="AF18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK18" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.05</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.87</v>
+        <v>1.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.52</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.54</v>
+        <v>3.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.69</v>
+        <v>1.16</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.39</v>
+        <v>5.53</v>
       </c>
       <c r="O20" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="P20" t="n">
-        <v>5.2</v>
+        <v>1.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.97</v>
+        <v>5.3</v>
       </c>
       <c r="R20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.45</v>
       </c>
-      <c r="S20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.41</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
         <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.45</v>
+        <v>3.74</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.62</v>
+        <v>1.12</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.41</v>
+        <v>2.46</v>
       </c>
       <c r="O21" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>5.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.94</v>
+        <v>2.91</v>
       </c>
       <c r="R21" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="S21" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="U21" t="n">
-        <v>2.29</v>
+        <v>3.17</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.52</v>
+        <v>1.72</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="P22" t="n">
-        <v>1.66</v>
+        <v>4.4</v>
       </c>
       <c r="Q22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z22" t="n">
         <v>4.4</v>
       </c>
-      <c r="R22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AA22" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.13</v>
+        <v>2.02</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.8</v>
+        <v>4.52</v>
       </c>
       <c r="O23" t="n">
         <v>3.7</v>
       </c>
       <c r="P23" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="R23" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T23" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
         <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4223,40 +4223,40 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="P24" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="Q24" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="R24" t="n">
         <v>2.75</v>
       </c>
-      <c r="R24" t="n">
-        <v>2.56</v>
-      </c>
       <c r="S24" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T24" t="n">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="V24" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z24" t="n">
         <v>6.7</v>
@@ -4265,22 +4265,22 @@
         <v>1.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="P26" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="R26" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="S26" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T26" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U26" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="V26" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="O27" t="n">
-        <v>5.85</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="R27" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="S27" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T27" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U27" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V27" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
         <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.13</v>
+        <v>4.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AK27" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,25 +1043,25 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1073,34 +1073,34 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1232,34 +1232,34 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,31 +1520,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.16</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.47</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.13</v>
+        <v>3.02</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="S7" t="n">
         <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W7" t="n">
         <v>1.14</v>
@@ -1553,47 +1553,47 @@
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.47</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>3.73</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.93</v>
+        <v>5.78</v>
       </c>
       <c r="R8" t="n">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>4.6</v>
+        <v>2.86</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.38</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.8</v>
+        <v>1.71</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.2</v>
+        <v>1.08</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="P9" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK9" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.47</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.17</v>
+        <v>5.16</v>
       </c>
       <c r="O10" t="n">
-        <v>6.2</v>
+        <v>4.25</v>
       </c>
       <c r="P10" t="n">
-        <v>11.22</v>
+        <v>1.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.54</v>
+        <v>5.13</v>
       </c>
       <c r="R10" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="S10" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.84</v>
+        <v>2.48</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>1.17</v>
       </c>
       <c r="O11" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.52</v>
+        <v>11.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.78</v>
+        <v>1.54</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>2.86</v>
+        <v>4.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.73</v>
+        <v>1.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.32</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.06</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.08</v>
+        <v>4.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.39</v>
+        <v>2.46</v>
       </c>
       <c r="O15" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>5.2</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.97</v>
+        <v>2.91</v>
       </c>
       <c r="R15" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="S15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="V15" t="n">
         <v>1.32</v>
       </c>
-      <c r="T15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.5</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.62</v>
+        <v>1.44</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.35</v>
+        <v>1.72</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.02</v>
+        <v>2.16</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="V16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.44</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.2</v>
+        <v>2.02</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.05</v>
+        <v>1.39</v>
       </c>
       <c r="O17" t="n">
-        <v>3.76</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.87</v>
+        <v>5.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.52</v>
+        <v>1.97</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T17" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
         <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.54</v>
+        <v>4.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.69</v>
+        <v>2.62</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.41</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>5.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.94</v>
+        <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
         <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>1.54</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.7</v>
+        <v>1.16</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>4.52</v>
       </c>
       <c r="O19" t="n">
         <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="U19" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="V19" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
         <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.46</v>
+        <v>1.41</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.62</v>
+        <v>5.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.91</v>
+        <v>1.94</v>
       </c>
       <c r="R21" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="S21" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="T21" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>3.17</v>
+        <v>2.29</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.92</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.83</v>
+        <v>2.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,43 +3905,43 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="O22" t="n">
         <v>3.76</v>
       </c>
       <c r="P22" t="n">
-        <v>4.4</v>
+        <v>2.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="R22" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="S22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U22" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V22" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
         <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.4</v>
+        <v>4.54</v>
       </c>
       <c r="AA22" t="n">
         <v>1.65</v>
@@ -3950,19 +3950,19 @@
         <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.52</v>
+        <v>4.35</v>
       </c>
       <c r="O23" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.4</v>
+        <v>5.02</v>
       </c>
       <c r="R23" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="U23" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.05</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>1.2</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1361,37 +1361,37 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>4.75</v>
+        <v>4.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="R6" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="U6" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
         <v>1.25</v>
@@ -1403,22 +1403,22 @@
         <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,31 +1520,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>5.16</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.02</v>
+        <v>5.13</v>
       </c>
       <c r="R7" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
         <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W7" t="n">
         <v>1.14</v>
@@ -1553,31 +1553,31 @@
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AG7" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.78</v>
+        <v>3.02</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>2.43</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.71</v>
+        <v>2.6</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>3.73</v>
+        <v>1.52</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.93</v>
+        <v>5.78</v>
       </c>
       <c r="R9" t="n">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>4.6</v>
+        <v>2.86</v>
       </c>
       <c r="U9" t="n">
-        <v>1.87</v>
+        <v>2.73</v>
       </c>
       <c r="V9" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.38</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.8</v>
+        <v>1.71</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.2</v>
+        <v>1.08</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.16</v>
+        <v>1.17</v>
       </c>
       <c r="O10" t="n">
-        <v>4.25</v>
+        <v>6.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.47</v>
+        <v>11.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.13</v>
+        <v>1.54</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="V10" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.48</v>
+        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="O11" t="n">
-        <v>6.2</v>
+        <v>4.15</v>
       </c>
       <c r="P11" t="n">
-        <v>11.22</v>
+        <v>3.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="R11" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="S11" t="n">
         <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="U11" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="V11" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.84</v>
+        <v>2.8</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.62</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>4.69</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.13</v>
+        <v>2.15</v>
       </c>
       <c r="R12" t="n">
-        <v>2.55</v>
+        <v>2.26</v>
       </c>
       <c r="S12" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="V12" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="W12" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.75</v>
+        <v>4.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.1</v>
+        <v>2.04</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.41</v>
+        <v>2.14</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,65 +2474,65 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.68</v>
+        <v>2.62</v>
       </c>
       <c r="O13" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="P13" t="n">
-        <v>4.69</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.15</v>
+        <v>3.13</v>
       </c>
       <c r="R13" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="S13" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="T13" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG13" t="n">
         <v>3.1</v>
       </c>
-      <c r="U13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.14</v>
+        <v>1.41</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.46</v>
+        <v>4.52</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.91</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.56</v>
-      </c>
       <c r="U15" t="n">
-        <v>3.17</v>
+        <v>2.68</v>
       </c>
       <c r="V15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.32</v>
       </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AE15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC15" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG15" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.72</v>
+        <v>5.53</v>
       </c>
       <c r="O16" t="n">
-        <v>3.76</v>
+        <v>4.15</v>
       </c>
       <c r="P16" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.16</v>
+        <v>5.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.4</v>
+        <v>3.74</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.02</v>
+        <v>1.12</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.39</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>3.76</v>
       </c>
       <c r="P17" t="n">
-        <v>5.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.97</v>
+        <v>2.52</v>
       </c>
       <c r="R17" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="U17" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
         <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.45</v>
+        <v>4.54</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.62</v>
+        <v>1.69</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>1.72</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8</v>
+        <v>2.16</v>
       </c>
       <c r="R18" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T18" t="n">
         <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.44</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.16</v>
+        <v>2.02</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.52</v>
+        <v>4.35</v>
       </c>
       <c r="O19" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.4</v>
+        <v>5.02</v>
       </c>
       <c r="R19" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="U19" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.05</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>5.53</v>
+        <v>2.46</v>
       </c>
       <c r="O20" t="n">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.3</v>
+        <v>2.91</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S20" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="U20" t="n">
-        <v>2.45</v>
+        <v>3.17</v>
       </c>
       <c r="V20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.44</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.12</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="O21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="P21" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="R21" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S21" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U21" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
         <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.05</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.87</v>
+        <v>1.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.52</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T22" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="U22" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.54</v>
+        <v>3.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.69</v>
+        <v>1.16</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.35</v>
+        <v>1.41</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.7</v>
+        <v>5.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.02</v>
+        <v>1.94</v>
       </c>
       <c r="R23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB23" t="n">
         <v>2.25</v>
       </c>
-      <c r="S23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2</v>
-      </c>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AE23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.11</v>
       </c>
-      <c r="AF23" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK23" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O25" t="n">
         <v>4.15</v>
       </c>
       <c r="P25" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R25" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S25" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T25" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U25" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O2" t="n">
         <v>2.75</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R3" t="n">
         <v>2.3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.56</v>
       </c>
       <c r="S3" t="n">
         <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V3" t="n">
         <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.57</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="n">
         <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
         <v>2.25</v>
@@ -935,13 +935,13 @@
         <v>1.66</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q4" t="n">
         <v>2.7</v>
@@ -1064,13 +1064,13 @@
         <v>2.33</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
         <v>1.08</v>
@@ -1079,28 +1079,28 @@
         <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AA4" t="n">
         <v>2.38</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.35</v>
+        <v>4.45</v>
       </c>
       <c r="AD4" t="n">
         <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
         <v>1.58</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1520,58 +1520,58 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.16</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="S7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T7" t="n">
         <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA7" t="n">
         <v>1.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AD7" t="n">
         <v>1.67</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF7" t="n">
         <v>1.44</v>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.14</v>
+        <v>2.29</v>
       </c>
       <c r="AK7" t="n">
         <v>1.1</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.02</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.22</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.52</v>
+        <v>4.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.78</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="T9" t="n">
-        <v>2.86</v>
+        <v>4.4</v>
       </c>
       <c r="U9" t="n">
-        <v>2.73</v>
+        <v>1.84</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.89</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.95</v>
+        <v>1.74</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.96</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.71</v>
+        <v>2.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.08</v>
+        <v>2.25</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.17</v>
+        <v>2.44</v>
       </c>
       <c r="O10" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
-        <v>11.22</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.54</v>
+        <v>2.95</v>
       </c>
       <c r="R10" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="S10" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>4.75</v>
+        <v>3.55</v>
       </c>
       <c r="U10" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="V10" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.25</v>
+        <v>2.43</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>1.41</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.84</v>
+        <v>2.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="O11" t="n">
-        <v>4.15</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>3.73</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="R11" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.33</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="O12" t="n">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>4.69</v>
+        <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="S12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA12" t="n">
         <v>1.29</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.48</v>
+        <v>1.81</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.04</v>
+        <v>3.14</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.62</v>
+        <v>1.61</v>
       </c>
       <c r="O13" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>4.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.13</v>
+        <v>2.12</v>
       </c>
       <c r="R13" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="S13" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="T13" t="n">
-        <v>4.25</v>
+        <v>3.15</v>
       </c>
       <c r="U13" t="n">
-        <v>1.87</v>
+        <v>2.39</v>
       </c>
       <c r="V13" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.79</v>
+        <v>1.44</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.41</v>
+        <v>2.21</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,28 +2633,28 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>3.53</v>
       </c>
       <c r="R14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U14" t="n">
         <v>2.3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.27</v>
       </c>
       <c r="V14" t="n">
         <v>1.53</v>
@@ -2669,28 +2669,28 @@
         <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.52</v>
+        <v>2.45</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="S15" t="n">
         <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
         <v>1.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.53</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>4.15</v>
+        <v>4.55</v>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>6.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.3</v>
+        <v>1.85</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.12</v>
+        <v>2.7</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.05</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="P17" t="n">
-        <v>2.87</v>
+        <v>1.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.52</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
         <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="U17" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="V17" t="n">
         <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.69</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.72</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.76</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.16</v>
+        <v>6.21</v>
       </c>
       <c r="R18" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="S18" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U18" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
         <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>2.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.02</v>
+        <v>1.12</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.02</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T19" t="n">
-        <v>2.89</v>
+        <v>3.21</v>
       </c>
       <c r="U19" t="n">
         <v>2.59</v>
       </c>
       <c r="V19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AC19" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.62</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.91</v>
+        <v>4.8</v>
       </c>
       <c r="R20" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T20" t="n">
-        <v>2.56</v>
+        <v>2.85</v>
       </c>
       <c r="U20" t="n">
-        <v>3.17</v>
+        <v>2.67</v>
       </c>
       <c r="V20" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.83</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,25 +3746,25 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="O21" t="n">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="P21" t="n">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="R21" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="S21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="U21" t="n">
         <v>2.41</v>
@@ -3773,37 +3773,37 @@
         <v>1.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
         <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.45</v>
+        <v>3.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>1.18</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O22" t="n">
         <v>3.8</v>
       </c>
-      <c r="O22" t="n">
-        <v>3.7</v>
-      </c>
       <c r="P22" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="R22" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="U22" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.44</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.16</v>
+        <v>2</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.41</v>
+        <v>2.06</v>
       </c>
       <c r="O23" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="P23" t="n">
-        <v>5.75</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.94</v>
+        <v>2.58</v>
       </c>
       <c r="R23" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S23" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T23" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U23" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="V23" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AD23" t="n">
         <v>1.47</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4223,16 +4223,16 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="O24" t="n">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="P24" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="R24" t="n">
         <v>2.75</v>
@@ -4256,25 +4256,25 @@
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z24" t="n">
         <v>6.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AB24" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AF24" t="n">
         <v>1.29</v>
@@ -4382,19 +4382,19 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O25" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="P25" t="n">
         <v>4.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S25" t="n">
         <v>1.23</v>
@@ -4406,7 +4406,7 @@
         <v>2.2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W25" t="n">
         <v>1.15</v>
@@ -4418,16 +4418,16 @@
         <v>1.12</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB25" t="n">
         <v>2.38</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AD25" t="n">
         <v>1.57</v>
@@ -4541,61 +4541,61 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="O26" t="n">
         <v>5.5</v>
       </c>
       <c r="P26" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="R26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.75</v>
       </c>
-      <c r="S26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U26" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="V26" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X26" t="n">
         <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.95</v>
+        <v>4.15</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AG26" t="n">
         <v>1.58</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK26" t="n">
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4709,7 +4709,7 @@
         <v>7.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="R27" t="n">
         <v>2.4</v>
@@ -4718,40 +4718,40 @@
         <v>1.27</v>
       </c>
       <c r="T27" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="U27" t="n">
-        <v>2.04</v>
+        <v>2.53</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
         <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
         <v>4.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF27" t="n">
         <v>1.92</v>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AK27" t="n">
-        <v>3.08</v>
+        <v>2.43</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4868,55 +4868,55 @@
         <v>2.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="R28" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="S28" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T28" t="n">
-        <v>2.63</v>
+        <v>3.08</v>
       </c>
       <c r="U28" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V28" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>1.23</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5027,52 +5027,52 @@
         <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="R29" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S29" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T29" t="n">
-        <v>3.07</v>
+        <v>2.92</v>
       </c>
       <c r="U29" t="n">
-        <v>2.13</v>
+        <v>2.56</v>
       </c>
       <c r="V29" t="n">
         <v>1.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
         <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AD29" t="n">
         <v>1.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
         <v>2.15</v>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="O2" t="n">
         <v>2.75</v>
       </c>
       <c r="P2" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
@@ -764,13 +764,13 @@
         <v>2.19</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AB2" t="n">
         <v>1.35</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AD2" t="n">
         <v>1.1</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46206.29166666666</v>
+        <v>46206.16666666666</v>
       </c>
     </row>
     <row r="3">
@@ -887,16 +887,16 @@
         <v>2.4</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S3" t="n">
         <v>1.25</v>
@@ -905,7 +905,7 @@
         <v>3.7</v>
       </c>
       <c r="U3" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
         <v>1.6</v>
@@ -929,7 +929,7 @@
         <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AD3" t="n">
         <v>1.66</v>
@@ -938,7 +938,7 @@
         <v>1.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG3" t="n">
         <v>2.66</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,55 +1052,55 @@
         <v>3.4</v>
       </c>
       <c r="Q4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.7</v>
       </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AA4" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.45</v>
+        <v>4.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE4" t="n">
         <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="R5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T5" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U5" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1367,25 +1367,25 @@
         <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>4.96</v>
+        <v>5.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
         <v>1.08</v>
@@ -1400,7 +1400,7 @@
         <v>3.28</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB6" t="n">
         <v>1.85</v>
@@ -1415,7 +1415,7 @@
         <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
         <v>1.76</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>1.15</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.53</v>
+        <v>12</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>1.42</v>
       </c>
       <c r="R7" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="T7" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V7" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.48</v>
+        <v>1.77</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>2.29</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>1.58</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.53</v>
+        <v>4.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>2.01</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>1.03</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>6.56</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>1.28</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.95</v>
+        <v>1.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.75</v>
+        <v>2.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.08</v>
+        <v>2.29</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="S9" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>8</v>
+        <v>4.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.25</v>
+        <v>2.29</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.74</v>
+        <v>2.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.4</v>
       </c>
-      <c r="AF9" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AG9" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.95</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.43</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.22</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.15</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>8.050000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.44</v>
       </c>
-      <c r="R11" t="n">
-        <v>3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AB11" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>2.36</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.06</v>
+        <v>2.29</v>
       </c>
       <c r="AK11" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.65</v>
+        <v>1.6</v>
       </c>
       <c r="O12" t="n">
         <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>2.14</v>
+        <v>4.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="R12" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="S12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.17</v>
       </c>
-      <c r="T12" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.14</v>
+        <v>2.06</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.61</v>
+        <v>2.31</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="S13" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="U13" t="n">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.11</v>
+        <v>3.14</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,16 +2633,16 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
         <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
         <v>2.21</v>
@@ -2660,16 +2660,16 @@
         <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="AA14" t="n">
         <v>1.54</v>
@@ -2681,7 +2681,7 @@
         <v>2.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AE14" t="n">
         <v>1.17</v>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
         <v>2.65</v>
@@ -2819,7 +2819,7 @@
         <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
@@ -2828,16 +2828,16 @@
         <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.44</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>4.55</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>6.65</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.85</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="U16" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
         <v>1.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.73</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AG17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.2</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>1.44</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="P18" t="n">
-        <v>1.55</v>
+        <v>6.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.21</v>
+        <v>1.85</v>
       </c>
       <c r="R18" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="U18" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="n">
         <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>2.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.12</v>
+        <v>2.7</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.2</v>
+        <v>1.67</v>
       </c>
       <c r="O19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>1.67</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="S19" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T19" t="n">
-        <v>3.21</v>
+        <v>2.63</v>
       </c>
       <c r="U19" t="n">
-        <v>2.59</v>
+        <v>2.36</v>
       </c>
       <c r="V19" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.45</v>
+        <v>4.69</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,28 +3587,28 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>1.41</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>4.55</v>
       </c>
       <c r="P20" t="n">
-        <v>1.67</v>
+        <v>6.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.8</v>
+        <v>1.93</v>
       </c>
       <c r="R20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.67</v>
       </c>
       <c r="V20" t="n">
         <v>1.48</v>
@@ -3617,34 +3617,34 @@
         <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.18</v>
+        <v>2.48</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.37</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="P21" t="n">
-        <v>6.9</v>
+        <v>1.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.86</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T21" t="n">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="U21" t="n">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
         <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.48</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.67</v>
+        <v>5.25</v>
       </c>
       <c r="O22" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P22" t="n">
-        <v>3.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.25</v>
+        <v>5.95</v>
       </c>
       <c r="R22" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="S22" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="T22" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="V22" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.16</v>
+        <v>2.3</v>
       </c>
       <c r="AK22" t="n">
-        <v>2</v>
+        <v>1.12</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4064,16 +4064,16 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="R23" t="n">
         <v>2.3</v>
@@ -4085,28 +4085,28 @@
         <v>3.4</v>
       </c>
       <c r="U23" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="V23" t="n">
         <v>1.55</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
         <v>4.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AC23" t="n">
         <v>2.63</v>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="AU23" s="3" t="n">
-        <v>46206.65625</v>
+        <v>46206.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -4232,13 +4232,13 @@
         <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="R24" t="n">
         <v>2.75</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T24" t="n">
         <v>5</v>
@@ -4247,7 +4247,7 @@
         <v>1.85</v>
       </c>
       <c r="V24" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="W24" t="n">
         <v>1.25</v>
@@ -4265,13 +4265,13 @@
         <v>1.31</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AC24" t="n">
         <v>1.78</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE24" t="n">
         <v>1.35</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4424,10 +4424,10 @@
         <v>1.53</v>
       </c>
       <c r="AB25" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC25" t="n">
         <v>2.38</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.34</v>
       </c>
       <c r="AD25" t="n">
         <v>1.57</v>
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="AU25" s="3" t="n">
-        <v>46206.83333333334</v>
+        <v>46206.85416666666</v>
       </c>
     </row>
     <row r="26">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="O26" t="n">
-        <v>5.5</v>
+        <v>4.55</v>
       </c>
       <c r="P26" t="n">
-        <v>9.5</v>
+        <v>6.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="R26" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T26" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.75</v>
       </c>
-      <c r="U26" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AD26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK26" t="n">
-        <v>4.32</v>
+        <v>2.43</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="P27" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S27" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T27" t="n">
-        <v>2.63</v>
+        <v>3.18</v>
       </c>
       <c r="U27" t="n">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="V27" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
         <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AE27" t="n">
         <v>1.11</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.43</v>
+        <v>4.1</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="O28" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P28" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q28" t="n">
         <v>2.95</v>
@@ -4898,16 +4898,16 @@
         <v>3.82</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE28" t="n">
         <v>1.11</v>
@@ -5018,37 +5018,37 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="O29" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="R29" t="n">
         <v>2.2</v>
       </c>
       <c r="S29" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T29" t="n">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="U29" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="V29" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W29" t="n">
         <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
         <v>1.25</v>
@@ -5057,22 +5057,22 @@
         <v>2.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE29" t="n">
         <v>1.11</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG29" t="n">
         <v>2.15</v>
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AK29" t="n">
         <v>1.4</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -702,26 +702,26 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -786,12 +786,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '90+7']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['79', '90+10']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46206.16666666666</v>
@@ -837,27 +837,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,114 +880,114 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>2.51</v>
       </c>
       <c r="P3" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="R3" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T3" t="n">
-        <v>3.7</v>
+        <v>2.36</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>1.12</v>
       </c>
-      <c r="Z3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46206.375</v>
+        <v>46206.29166666666</v>
       </c>
     </row>
     <row r="4">
@@ -996,27 +996,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="R4" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2.46</v>
+        <v>3.7</v>
       </c>
       <c r="U4" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="W4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.04</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.15</v>
+        <v>2.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.16</v>
+        <v>1.66</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.73</v>
+        <v>2.66</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46206.41666666666</v>
+        <v>46206.375</v>
       </c>
     </row>
     <row r="5">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="R5" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="S5" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="U5" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.03</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.61</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.15</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>12</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.42</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="S7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.17</v>
       </c>
-      <c r="T7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.77</v>
+        <v>2.36</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.06</v>
+        <v>2.29</v>
       </c>
       <c r="AK7" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="P8" t="n">
-        <v>4.65</v>
+        <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.01</v>
+        <v>1.42</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
         <v>1.17</v>
       </c>
       <c r="T8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="V8" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.56</v>
+        <v>5.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.98</v>
+        <v>1.77</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.29</v>
+        <v>5.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.44</v>
+        <v>1.58</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>4.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.01</v>
       </c>
       <c r="R9" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="S9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.14</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.75</v>
+        <v>6.56</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AB9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK9" t="n">
         <v>2.29</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>2.44</v>
       </c>
       <c r="O11" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.53</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.6</v>
+        <v>2.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P12" t="n">
-        <v>4.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.12</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="S12" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="U12" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.98</v>
+        <v>6.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.29</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.63</v>
+        <v>1.87</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.06</v>
+        <v>3.14</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="O13" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>4.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="R13" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="S13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.17</v>
       </c>
-      <c r="T13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.14</v>
+        <v>2.06</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.41</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>3.27</v>
       </c>
       <c r="U15" t="n">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.92</v>
+        <v>3.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>1.67</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S16" t="n">
         <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,65 +3269,65 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>5.25</v>
       </c>
       <c r="O18" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>6.25</v>
+        <v>1.53</v>
       </c>
       <c r="Q18" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.85</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.13</v>
+        <v>2.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.7</v>
+        <v>1.12</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.67</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AB19" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>2.41</v>
       </c>
       <c r="O21" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="S21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
-        <v>3.27</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>2.59</v>
+        <v>2.96</v>
       </c>
       <c r="V21" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.72</v>
+        <v>2.92</v>
       </c>
       <c r="AA21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="O22" t="n">
         <v>3.9</v>
       </c>
       <c r="P22" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.95</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S22" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>2.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1020,96 +1020,96 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P4" t="n">
         <v>2.4</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.55</v>
-      </c>
       <c r="Q4" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T4" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
         <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.66</v>
+        <v>2.89</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['64', '75']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46206.375</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46206.41666666666</v>
@@ -1361,22 +1361,22 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>5.1</v>
+        <v>4.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="R6" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
         <v>3</v>
@@ -1388,34 +1388,34 @@
         <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB6" t="n">
         <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE6" t="n">
         <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG6" t="n">
         <v>1.76</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.15</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>12</v>
+        <v>1.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.42</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>2.23</v>
       </c>
       <c r="S8" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>1.97</v>
+        <v>2.82</v>
       </c>
       <c r="V8" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.31</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.92</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.96</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.82</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>5.1</v>
+        <v>1.12</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="P9" t="n">
-        <v>4.65</v>
+        <v>12</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.01</v>
+        <v>1.42</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
         <v>1.17</v>
       </c>
       <c r="T9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="V9" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.56</v>
+        <v>5.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.98</v>
+        <v>1.77</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.29</v>
+        <v>5.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>1.58</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.53</v>
+        <v>4.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>2.01</v>
       </c>
       <c r="R10" t="n">
-        <v>2.23</v>
+        <v>2.8</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="U10" t="n">
-        <v>2.82</v>
+        <v>1.83</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>6.56</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.89</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="AD10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.75</v>
+        <v>2.98</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.12</v>
+        <v>2.29</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.67</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
         <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="U16" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.69</v>
+        <v>3.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>2.41</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>2.41</v>
+        <v>1.97</v>
       </c>
       <c r="S17" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
-        <v>2.45</v>
+        <v>2.96</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.08</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.41</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>6.6</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.93</v>
+        <v>4.8</v>
       </c>
       <c r="R20" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="S20" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="U20" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V20" t="n">
         <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.48</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.41</v>
+        <v>1.67</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U21" t="n">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.92</v>
+        <v>4.69</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>2.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,34 +3905,34 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.9</v>
+        <v>1.41</v>
       </c>
       <c r="O22" t="n">
-        <v>3.9</v>
+        <v>4.55</v>
       </c>
       <c r="P22" t="n">
-        <v>1.74</v>
+        <v>6.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>1.93</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U22" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
@@ -3941,28 +3941,28 @@
         <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.2</v>
+        <v>2.48</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="S7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.2</v>
       </c>
-      <c r="T7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Z7" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.11</v>
+        <v>2.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.36</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>2.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,16 +1647,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1668,118 +1668,118 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>2.44</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
         <v>6</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-1</v>
-      </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46206.54166666666</v>
@@ -1838,61 +1838,61 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="O9" t="n">
         <v>6.2</v>
       </c>
       <c r="P9" t="n">
-        <v>12</v>
+        <v>11.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T9" t="n">
         <v>4.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
         <v>1.96</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AE9" t="n">
         <v>1.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
         <v>1.77</v>
@@ -1911,7 +1911,7 @@
         <v>1.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1974,130 +1974,130 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="O10" t="n">
-        <v>4.2</v>
+        <v>4.95</v>
       </c>
       <c r="P10" t="n">
-        <v>4.65</v>
+        <v>5.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="R10" t="n">
         <v>2.8</v>
       </c>
       <c r="S10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.56</v>
+        <v>7.18</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB10" t="n">
         <v>3.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
         <v>1.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '6', '18', '33', '51']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.29</v>
+        <v>2.58</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46206.54166666666</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.44</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>1.49</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T11" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V11" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AG11" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>2.29</v>
       </c>
-      <c r="AC11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2321,19 +2321,19 @@
         <v>3.55</v>
       </c>
       <c r="P12" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="S12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T12" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U12" t="n">
         <v>1.91</v>
@@ -2342,7 +2342,7 @@
         <v>1.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -2351,7 +2351,7 @@
         <v>1.04</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="AA12" t="n">
         <v>1.29</v>
@@ -2360,19 +2360,19 @@
         <v>3.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="R13" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="U13" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="V13" t="n">
         <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.98</v>
+        <v>4.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2633,19 +2633,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="S14" t="n">
         <v>1.27</v>
@@ -2660,7 +2660,7 @@
         <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
@@ -2669,28 +2669,28 @@
         <v>1.13</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD14" t="n">
         <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2795,61 +2795,61 @@
         <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S15" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T15" t="n">
-        <v>3.27</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="V15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>6.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
         <v>1.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AC16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK16" t="n">
         <v>2.7</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="R17" t="n">
         <v>1.97</v>
@@ -3143,16 +3143,16 @@
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
         <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
         <v>3.58</v>
@@ -3161,7 +3161,7 @@
         <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF17" t="n">
         <v>1.75</v>
@@ -3269,22 +3269,22 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P18" t="n">
         <v>1.53</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.95</v>
+        <v>5.85</v>
       </c>
       <c r="R18" t="n">
         <v>2.2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
         <v>3</v>
@@ -3293,34 +3293,34 @@
         <v>2.75</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
         <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC18" t="n">
         <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
         <v>1.83</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,52 +3428,52 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="O19" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>6.25</v>
+        <v>6.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R19" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AD19" t="n">
         <v>1.48</v>
@@ -3485,7 +3485,7 @@
         <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P20" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
-        <v>2.41</v>
+        <v>2.16</v>
       </c>
       <c r="S20" t="n">
         <v>1.35</v>
       </c>
       <c r="T20" t="n">
-        <v>2.84</v>
+        <v>3.19</v>
       </c>
       <c r="U20" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
         <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
         <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="Q21" t="n">
         <v>2.25</v>
@@ -3761,43 +3761,43 @@
         <v>2.28</v>
       </c>
       <c r="S21" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T21" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
         <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.69</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
         <v>2.63</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF21" t="n">
         <v>1.61</v>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK21" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.41</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>4.55</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>6.6</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.93</v>
+        <v>4.17</v>
       </c>
       <c r="R22" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="S22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.29</v>
       </c>
-      <c r="T22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AK22" t="n">
-        <v>2.48</v>
+        <v>1.25</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P23" t="n">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S23" t="n">
         <v>1.29</v>
       </c>
       <c r="T23" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U23" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="V23" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG23" t="n">
         <v>2.18</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.45</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>1.26</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4223,34 +4223,34 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="O24" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="R24" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S24" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T24" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V24" t="n">
         <v>1.79</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -4259,19 +4259,19 @@
         <v>1.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.7</v>
+        <v>6.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE24" t="n">
         <v>1.35</v>
@@ -4280,7 +4280,7 @@
         <v>1.29</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,19 +4382,19 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P25" t="n">
         <v>4.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R25" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="S25" t="n">
         <v>1.23</v>
@@ -4406,7 +4406,7 @@
         <v>2.2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W25" t="n">
         <v>1.15</v>
@@ -4427,7 +4427,7 @@
         <v>2.37</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
         <v>1.57</v>
@@ -4439,7 +4439,7 @@
         <v>1.53</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="O26" t="n">
-        <v>4.55</v>
+        <v>5.75</v>
       </c>
       <c r="P26" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="R26" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="S26" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T26" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U26" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X26" t="n">
         <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.05</v>
+        <v>4.93</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.43</v>
+        <v>4</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="O27" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="P27" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="R27" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S27" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T27" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="U27" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="V27" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
         <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK27" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4859,19 +4859,19 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="O28" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S28" t="n">
         <v>1.25</v>
@@ -4901,7 +4901,7 @@
         <v>1.56</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
         <v>2.75</v>
@@ -4910,13 +4910,13 @@
         <v>1.36</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O29" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="P29" t="n">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.22</v>
+        <v>2.82</v>
       </c>
       <c r="R29" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.29</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.31</v>
       </c>
       <c r="AE29" t="n">
         <v>1.11</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,139 +1488,139 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.25</v>
+        <v>1.47</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="P7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q7" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '6', '18', '33', '51']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.08</v>
+        <v>2.58</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46206.54166666666</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,28 +1647,28 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1679,107 +1679,107 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.44</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>1.49</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.23</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
         <v>2.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="U8" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AG8" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '26', '45+1']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.55</v>
+        <v>2.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AN8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AO8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AP8" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AS8" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="AT8" t="n">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46206.54166666666</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1834,111 +1834,111 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.13</v>
+        <v>5.25</v>
       </c>
       <c r="O9" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="P9" t="n">
-        <v>11.22</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.44</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="S9" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="T9" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>2.44</v>
       </c>
       <c r="V9" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.08</v>
       </c>
-      <c r="Z9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46206.54166666666</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,28 +1965,28 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1997,107 +1997,107 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="O10" t="n">
-        <v>4.95</v>
+        <v>6.2</v>
       </c>
       <c r="P10" t="n">
-        <v>5.8</v>
+        <v>11.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="S10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T10" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.18</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.21</v>
+        <v>1.84</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>['11', '48', '90+3']</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>2.9</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>['2', '6', '18', '33', '51']</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>['24']</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AR10" t="n">
-        <v>1.64</v>
+        <v>0.62</v>
       </c>
       <c r="AS10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AT10" t="n">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46206.54166666666</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,16 +2124,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -2145,118 +2145,118 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>2.44</v>
       </c>
       <c r="O11" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
-        <v>1.49</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>3.23</v>
       </c>
       <c r="R11" t="n">
         <v>2.5</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="W11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.18</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AF11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
         <v>6</v>
       </c>
-      <c r="AA11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="AN11" t="n">
         <v>2</v>
       </c>
-      <c r="AD11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>-1</v>
-      </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46206.54166666666</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,139 +2283,139 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.31</v>
+        <v>1.57</v>
       </c>
       <c r="O12" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="R12" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="T12" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="U12" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="V12" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.1</v>
+        <v>4.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.81</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.26</v>
+        <v>2.21</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '46', '50', '69']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56', '65', '81', '90+1']</t>
         </is>
       </c>
       <c r="AJ12" t="n">
         <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46206.58333333334</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,139 +2442,139 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.57</v>
+        <v>2.31</v>
       </c>
       <c r="O13" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P13" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S13" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="T13" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="U13" t="n">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.3</v>
+        <v>7.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.55</v>
+        <v>1.81</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.21</v>
+        <v>3.26</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47', '65']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '30', '60', '66', '68']</t>
         </is>
       </c>
       <c r="AJ13" t="n">
         <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO13" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46206.58333333334</v>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2712,28 +2712,28 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP14" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46206.625</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="R15" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="S15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>3.19</v>
       </c>
       <c r="U15" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="V15" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
         <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
         <v>1.13</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.44</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>6.35</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.85</v>
+        <v>4.8</v>
       </c>
       <c r="R16" t="n">
         <v>2.38</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="U16" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="V16" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.7</v>
+        <v>1.18</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.71</v>
+        <v>1.53</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.22</v>
+        <v>5.85</v>
       </c>
       <c r="R17" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="S17" t="n">
         <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.1</v>
+        <v>3.84</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,61 +3269,61 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>1.43</v>
       </c>
       <c r="O18" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.53</v>
+        <v>6.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.85</v>
+        <v>1.87</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.84</v>
+        <v>4.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="n">
         <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
         <v>1.85</v>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.12</v>
+        <v>2.76</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="P19" t="n">
-        <v>6.12</v>
+        <v>4.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="S19" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="V19" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.76</v>
+        <v>2.1</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,61 +3587,61 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>1.44</v>
       </c>
       <c r="O20" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.61</v>
+        <v>6.35</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.5</v>
+        <v>1.85</v>
       </c>
       <c r="R20" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="S20" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="V20" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG20" t="n">
         <v>1.95</v>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.12</v>
+        <v>2.7</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>4.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q21" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="R21" t="n">
         <v>2.25</v>
       </c>
-      <c r="R21" t="n">
-        <v>2.28</v>
-      </c>
       <c r="S21" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U21" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
         <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>2.71</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.17</v>
+        <v>3.22</v>
       </c>
       <c r="R22" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T22" t="n">
-        <v>3.08</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
         <v>2.85</v>
@@ -4238,49 +4238,49 @@
         <v>2.8</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T24" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="V24" t="n">
         <v>1.79</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.55</v>
+        <v>6.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC24" t="n">
         <v>1.81</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF24" t="n">
         <v>1.29</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="O26" t="n">
-        <v>5.75</v>
+        <v>4.7</v>
       </c>
       <c r="P26" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="R26" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="S26" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T26" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U26" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V26" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="W26" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
         <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.93</v>
+        <v>4.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK26" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="O27" t="n">
-        <v>4.7</v>
+        <v>5.75</v>
       </c>
       <c r="P27" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="S27" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T27" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U27" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V27" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
         <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.05</v>
+        <v>4.93</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK27" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,139 +1488,139 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
+      <c r="AN7" t="n">
         <v>4</v>
       </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>['2', '6', '18', '33', '51']</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>['24']</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>3</v>
-      </c>
       <c r="AO7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AP7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.81</v>
+        <v>0.67</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.64</v>
+        <v>1.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46206.54166666666</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,28 +1647,28 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1679,34 +1679,34 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T8" t="n">
         <v>4.5</v>
       </c>
-      <c r="O8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.9</v>
-      </c>
       <c r="U8" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="V8" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
@@ -1715,71 +1715,71 @@
         <v>1.08</v>
       </c>
       <c r="Z8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>['11', '48', '90+3']</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP8" t="n">
         <v>6</v>
       </c>
-      <c r="AA8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>['21']</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>['20', '26', '45+1']</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>18</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>1.33</v>
+        <v>2.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.95</v>
+        <v>0.62</v>
       </c>
       <c r="AS8" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="AT8" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46206.54166666666</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,28 +1806,28 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1838,107 +1838,107 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5.25</v>
+        <v>1.47</v>
       </c>
       <c r="O9" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="P9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q9" t="n">
-        <v>6</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '6', '18', '33', '51']</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.08</v>
+        <v>2.58</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AN9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AP9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.67</v>
+        <v>1.81</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.1</v>
+        <v>1.64</v>
       </c>
       <c r="AS9" t="n">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="AT9" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46206.54166666666</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,28 +1965,28 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
         <v>3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1997,34 +1997,34 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.13</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
-        <v>11.22</v>
+        <v>1.49</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.44</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T10" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="V10" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
@@ -2033,71 +2033,71 @@
         <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.3</v>
       </c>
-      <c r="AB10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.77</v>
+        <v>2.47</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>['11', '48', '90+3']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '26', '45+1']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>2.29</v>
       </c>
       <c r="AK10" t="n">
-        <v>5.3</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AO10" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.9</v>
+        <v>1.33</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.62</v>
+        <v>1.95</v>
       </c>
       <c r="AS10" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="AT10" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46206.54166666666</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,139 +2283,139 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="L12" t="n">
-        <v>4</v>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.57</v>
+        <v>2.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P12" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S12" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="T12" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="U12" t="n">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.3</v>
+        <v>7.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.55</v>
+        <v>1.81</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.21</v>
+        <v>3.26</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>['14', '46', '50', '69']</t>
+          <t>['47', '65']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>['56', '65', '81', '90+1']</t>
+          <t>['3', '30', '60', '66', '68']</t>
         </is>
       </c>
       <c r="AJ12" t="n">
         <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AN12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.03</v>
+        <v>1.56</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.16</v>
+        <v>2.86</v>
       </c>
       <c r="AS12" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AT12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46206.58333333334</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,31 +2442,31 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2474,107 +2474,107 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.31</v>
+        <v>1.57</v>
       </c>
       <c r="O13" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="R13" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="T13" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="U13" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="V13" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.1</v>
+        <v>4.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.81</v>
+        <v>2.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.26</v>
+        <v>2.21</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>['47', '65']</t>
+          <t>['14', '46', '50', '69']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>['3', '30', '60', '66', '68']</t>
+          <t>['56', '65', '81', '90+1']</t>
         </is>
       </c>
       <c r="AJ13" t="n">
         <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AO13" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AP13" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.56</v>
+        <v>2.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.86</v>
+        <v>2.16</v>
       </c>
       <c r="AS13" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AT13" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46206.58333333334</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,22 +2760,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2788,111 +2788,111 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>1.43</v>
       </c>
       <c r="O15" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1.61</v>
+        <v>6.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.5</v>
+        <v>1.87</v>
       </c>
       <c r="R15" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>['8', '17', '23']</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.1</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.12</v>
+        <v>2.76</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP15" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU15" s="3" t="n">
         <v>46206.65625</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,22 +2919,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2947,111 +2947,111 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>1.65</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>4.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.8</v>
+        <v>2.25</v>
       </c>
       <c r="R16" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S16" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T16" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN16" t="n">
         <v>2</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>-1</v>
-      </c>
       <c r="AO16" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP16" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>46206.65625</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,16 +3078,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3099,118 +3099,118 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.85</v>
+        <v>4.17</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U17" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AE17" t="n">
         <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ17" t="n">
-        <v>2.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN17" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO17" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP17" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46206.65625</v>
@@ -3237,22 +3237,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -3261,115 +3261,115 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.43</v>
       </c>
-      <c r="O18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P18" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.49</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.3</v>
+        <v>3.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AE18" t="n">
         <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
         <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47', '82']</t>
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.76</v>
+        <v>1.12</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN18" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO18" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP18" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AU18" s="3" t="n">
         <v>46206.65625</v>
@@ -3396,139 +3396,139 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>4.4</v>
+        <v>2.71</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.25</v>
+        <v>3.22</v>
       </c>
       <c r="R19" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="S19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>['67', '85']</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR19" t="n">
         <v>1.27</v>
       </c>
-      <c r="T19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU19" s="3" t="n">
         <v>46206.65625</v>
@@ -3555,96 +3555,96 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.44</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>6.35</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.85</v>
+        <v>4.8</v>
       </c>
       <c r="R20" t="n">
         <v>2.38</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="U20" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="V20" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3653,41 +3653,41 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '78']</t>
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.7</v>
+        <v>1.18</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN20" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP20" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU20" s="3" t="n">
         <v>46206.65625</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,139 +3714,139 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>1.44</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P21" t="n">
-        <v>1.91</v>
+        <v>6.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.17</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S21" t="n">
         <v>1.3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="U21" t="n">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="V21" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
         <v>4.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE21" t="n">
         <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82', '85']</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '69', '77', '90+2']</t>
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN21" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO21" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU21" s="3" t="n">
         <v>46206.65625</v>
@@ -3873,25 +3873,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -3901,62 +3901,62 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.71</v>
+        <v>1.61</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="S22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T22" t="n">
-        <v>2.65</v>
+        <v>3.19</v>
       </c>
       <c r="U22" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="V22" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF22" t="n">
         <v>1.75</v>
@@ -3971,41 +3971,41 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN22" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO22" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP22" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AU22" s="3" t="n">
         <v>46206.65625</v>
@@ -4041,16 +4041,16 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39', '41']</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AJ23" t="n">
@@ -4143,28 +4143,28 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN23" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP23" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU23" s="3" t="n">
         <v>46206.66666666666</v>
@@ -4200,16 +4200,16 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '42']</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '36']</t>
         </is>
       </c>
       <c r="AJ24" t="n">
@@ -4302,28 +4302,28 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN24" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO24" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP24" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU24" s="3" t="n">
         <v>46206.67708333334</v>

--- a/jogos_2026-07-03.xlsx
+++ b/jogos_2026-07-03.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,139 +1647,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN8" t="n">
         <v>2</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="O8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>['11', '48', '90+3']</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
       <c r="AO8" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AP8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.9</v>
+        <v>1.52</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.62</v>
+        <v>1.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AT8" t="n">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46206.54166666666</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,28 +2124,28 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2156,68 +2156,68 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.44</v>
+        <v>1.13</v>
       </c>
       <c r="O11" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>11.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.23</v>
+        <v>1.44</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="S11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.25</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.14</v>
-      </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.54</v>
+        <v>1.84</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.53</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['11', '48', '90+3']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2226,37 +2226,37 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.48</v>
+        <v>5.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP11" t="n">
         <v>6</v>
       </c>
-      <c r="AN11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>10</v>
-      </c>
       <c r="AQ11" t="n">
-        <v>1.52</v>
+        <v>2.9</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.4</v>
+        <v>0.62</v>
       </c>
       <c r="AS11" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="AT11" t="n">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46206.54166666666</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,31 +2283,31 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2315,107 +2315,107 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.31</v>
+        <v>1.57</v>
       </c>
       <c r="O12" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="R12" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="T12" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="U12" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="V12" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.1</v>
+        <v>4.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.81</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.26</v>
+        <v>2.21</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>['47', '65']</t>
+          <t>['14', '46', '50', '69']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>['3', '30', '60', '66', '68']</t>
+          <t>['56', '65', '81', '90+1']</t>
         </is>
       </c>
       <c r="AJ12" t="n">
         <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AO12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AP12" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.56</v>
+        <v>2.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.86</v>
+        <v>2.16</v>
       </c>
       <c r="AS12" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AT12" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46206.58333333334</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,139 +2442,139 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
         <v>3</v>
       </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.57</v>
+        <v>2.31</v>
       </c>
       <c r="O13" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P13" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S13" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="T13" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="U13" t="n">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.3</v>
+        <v>7.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.55</v>
+        <v>1.81</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.21</v>
+        <v>3.26</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>['14', '46', '50', '69']</t>
+          <t>['47', '65']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>['56', '65', '81', '90+1']</t>
+          <t>['3', '30', '60', '66', '68']</t>
         </is>
       </c>
       <c r="AJ13" t="n">
         <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AN13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AO13" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.03</v>
+        <v>1.56</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.16</v>
+        <v>2.86</v>
       </c>
       <c r="AS13" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AT13" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46206.58333333334</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,139 +2760,139 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
         <v>3</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P15" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="AN15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>1.49</v>
       </c>
-      <c r="W15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>['8', '17', '23']</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>2.64</v>
-      </c>
       <c r="AR15" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.64</v>
       </c>
       <c r="AS15" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="AT15" t="n">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="AU15" s="3" t="n">
         <v>46206.65625</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,22 +2919,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2951,68 +2951,68 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="O16" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>4.4</v>
+        <v>6.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="R16" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="S16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['8', '17', '23']</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -3021,37 +3021,37 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.1</v>
+        <v>2.76</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AN16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AP16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.72</v>
+        <v>2.64</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AT16" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>46206.65625</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,139 +3078,139 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z17" t="n">
         <v>3.4</v>
       </c>
-      <c r="P17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>['16', '78']</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN17" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AO17" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AP17" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1</v>
+        <v>1.93</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="AS17" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="AT17" t="n">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46206.65625</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,139 +3237,139 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AC18" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AE18" t="n">
         <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>['47', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>2.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO18" t="n">
         <v>6</v>
       </c>
-      <c r="AO18" t="n">
-        <v>10</v>
-      </c>
       <c r="AP18" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.63</v>
+        <v>2.34</v>
       </c>
       <c r="AS18" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="AT18" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="AU18" s="3" t="n">
         <v>46206.65625</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,139 +3396,139 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.71</v>
+        <v>1.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.22</v>
+        <v>5.85</v>
       </c>
       <c r="R19" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
         <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>3.84</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>['67', '85']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['47', '82']</t>
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.71</v>
+        <v>1.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.27</v>
+        <v>2.63</v>
       </c>
       <c r="AS19" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="AT19" t="n">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="AU19" s="3" t="n">
         <v>46206.65625</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,139 +3555,139 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>['16', '78']</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>4</v>
-      </c>
       <c r="AO20" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AP20" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="AT20" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AU20" s="3" t="n">
         <v>46206.65625</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,19 +3714,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -3746,107 +3746,107 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="O21" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>6.35</v>
+        <v>2.71</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="R21" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>2.49</v>
+        <v>2.96</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
         <v>1.95</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>['82', '85']</t>
+          <t>['67', '85']</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>['14', '69', '77', '90+2']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN21" t="n">
         <v>5</v>
       </c>
       <c r="AO21" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AP21" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.49</v>
+        <v>1.71</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AS21" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="AT21" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="AU21" s="3" t="n">
         <v>46206.65625</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,19 +3873,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3894,10 +3894,10 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -3905,107 +3905,107 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.4</v>
+        <v>1.44</v>
       </c>
       <c r="O22" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.61</v>
+        <v>6.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>1.85</v>
       </c>
       <c r="R22" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="S22" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T22" t="n">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="U22" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="V22" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG22" t="n">
         <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82', '85']</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['14', '69', '77', '90+2']</t>
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.12</v>
+        <v>2.7</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AN22" t="n">
         <v>5</v>
       </c>
       <c r="AO22" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.49</v>
+        <v>2.49</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AS22" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="AT22" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="AU22" s="3" t="n">
         <v>46206.65625</v>
@@ -4359,42 +4359,42 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="O25" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="R25" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="S25" t="n">
         <v>1.23</v>
@@ -4421,68 +4421,68 @@
         <v>4.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE25" t="n">
         <v>1.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81', '90+1']</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1', '90+3']</t>
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN25" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO25" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP25" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU25" s="3" t="n">
         <v>46206.85416666666</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="O26" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="R26" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="S26" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="T26" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="U26" t="n">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="V26" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X26" t="n">
         <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.05</v>
+        <v>5.63</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AB26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>1.08</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.3</v>
+        <v>4.92</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="O27" t="n">
-        <v>5.75</v>
+        <v>4.7</v>
       </c>
       <c r="P27" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="R27" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="S27" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T27" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U27" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V27" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
         <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.93</v>
+        <v>4.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK27" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
